--- a/Fantasy_Grimdark_Scale_Fully_Scored.xlsx
+++ b/Fantasy_Grimdark_Scale_Fully_Scored.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="594" uniqueCount="273">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="594" uniqueCount="271">
   <si>
     <t xml:space="preserve">Fantasy Darkness Scale: Methodology</t>
   </si>
@@ -204,7 +204,7 @@
     <t xml:space="preserve">T. J. Klune</t>
   </si>
   <si>
-    <t xml:space="preserve">Partial</t>
+    <t xml:space="preserve">No</t>
   </si>
   <si>
     <t xml:space="preserve">Institutional prejudice is real, but empathy and care can reform lives.</t>
@@ -216,9 +216,6 @@
     <t xml:space="preserve">Alexandra Rowland</t>
   </si>
   <si>
-    <t xml:space="preserve">No</t>
-  </si>
-  <si>
     <t xml:space="preserve">Hopepunk through resistance, storytelling and collective action.</t>
   </si>
   <si>
@@ -766,9 +763,6 @@
   </si>
   <si>
     <t xml:space="preserve">George R. R. Martin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rare</t>
   </si>
   <si>
     <t xml:space="preserve">Institutions reward violence and compromise while idealism rarely transforms the system.</t>
@@ -858,6 +852,7 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -875,15 +870,15 @@
       <family val="0"/>
     </font>
     <font>
-      <sz val="11"/>
+      <b val="true"/>
+      <sz val="16"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
-      <sz val="16"/>
-      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
       <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
@@ -945,7 +940,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="21">
+  <cellStyleXfs count="20">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -969,69 +964,64 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
   </cellStyleXfs>
   <cellXfs count="12">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="20" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="20" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="20" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="20" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="20" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
-  <cellStyles count="7">
+  <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Comma" xfId="15" builtinId="3"/>
     <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
     <cellStyle name="Currency" xfId="17" builtinId="4"/>
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
-    <cellStyle name="Normal" xfId="20"/>
   </cellStyles>
   <dxfs count="102">
     <dxf>
@@ -2194,11 +2184,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="96515678"/>
-        <c:axId val="27720482"/>
+        <c:axId val="43734253"/>
+        <c:axId val="44364566"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="96515678"/>
+        <c:axId val="43734253"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2243,7 +2233,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="27720482"/>
+        <c:crossAx val="44364566"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2251,7 +2241,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="27720482"/>
+        <c:axId val="44364566"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2296,7 +2286,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="96515678"/>
+        <c:crossAx val="43734253"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2553,9 +2543,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>610920</xdr:colOff>
+      <xdr:colOff>609480</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>190080</xdr:rowOff>
+      <xdr:rowOff>188640</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -2563,8 +2553,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="7518960" y="440640"/>
-        <a:ext cx="4891680" cy="3428640"/>
+        <a:off x="7518960" y="438120"/>
+        <a:ext cx="4890240" cy="3427200"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -2737,373 +2727,373 @@
   <dimension ref="A1:H24"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="58"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="14"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="3" t="s">
+      <c r="C3" s="3"/>
+      <c r="D3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2" t="s">
+      <c r="C4" s="3"/>
+      <c r="D4" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="4" t="n">
+      <c r="E4" s="5" t="n">
         <v>0.15</v>
       </c>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2" t="s">
+      <c r="C5" s="3"/>
+      <c r="D5" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="4" t="n">
+      <c r="E5" s="5" t="n">
         <v>0.15</v>
       </c>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2" t="s">
+      <c r="C6" s="3"/>
+      <c r="D6" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E6" s="4" t="n">
+      <c r="E6" s="5" t="n">
         <v>0.15</v>
       </c>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-    </row>
-    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+    </row>
+    <row r="7" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2" t="s">
+      <c r="C7" s="3"/>
+      <c r="D7" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E7" s="4" t="n">
+      <c r="E7" s="5" t="n">
         <v>0.15</v>
       </c>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="s">
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2" t="s">
+      <c r="C8" s="3"/>
+      <c r="D8" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="E8" s="4" t="n">
+      <c r="E8" s="5" t="n">
         <v>0.15</v>
       </c>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2" t="s">
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2" t="s">
+      <c r="C9" s="3"/>
+      <c r="D9" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="E9" s="4" t="n">
+      <c r="E9" s="5" t="n">
         <v>0.15</v>
       </c>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
-    </row>
-    <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2" t="s">
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+    </row>
+    <row r="10" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2" t="s">
+      <c r="C10" s="3"/>
+      <c r="D10" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E10" s="4" t="n">
+      <c r="E10" s="5" t="n">
         <v>0.1</v>
       </c>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2" t="s">
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="3"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2" t="s">
+      <c r="C11" s="3"/>
+      <c r="D11" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E11" s="4" t="n">
+      <c r="E11" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2" t="s">
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
+      <c r="H11" s="3"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2"/>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="3" t="s">
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
+      <c r="H12" s="3"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="3"/>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
+      <c r="H13" s="3"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="2" t="n">
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3"/>
+      <c r="H14" s="3"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="2" t="n">
+      <c r="C15" s="3"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="3"/>
+      <c r="H15" s="3"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="2" t="n">
+      <c r="C16" s="3"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="3"/>
+      <c r="H16" s="3"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B17" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="2" t="n">
+      <c r="C17" s="3"/>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="3"/>
+      <c r="H17" s="3"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="B18" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="2" t="n">
+      <c r="C18" s="3"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="3"/>
+      <c r="H18" s="3"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B19" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="2" t="n">
+      <c r="C19" s="3"/>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3"/>
+      <c r="H19" s="3"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B20" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="2" t="n">
+      <c r="C20" s="3"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="3"/>
+      <c r="H20" s="3"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="B21" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
-      <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
-      <c r="H21" s="2"/>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="2" t="n">
+      <c r="C21" s="3"/>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="3"/>
+      <c r="H21" s="3"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="B22" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
-      <c r="E22" s="2"/>
-      <c r="F22" s="2"/>
-      <c r="G22" s="2"/>
-      <c r="H22" s="2"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="2" t="n">
+      <c r="C22" s="3"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3"/>
+      <c r="H22" s="3"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="B23" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
-      <c r="H23" s="2"/>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="2" t="n">
+      <c r="C23" s="3"/>
+      <c r="D23" s="3"/>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="3"/>
+      <c r="H23" s="3"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="B24" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
-      <c r="E24" s="2"/>
-      <c r="F24" s="2"/>
-      <c r="G24" s="2"/>
-      <c r="H24" s="2"/>
+      <c r="C24" s="3"/>
+      <c r="D24" s="3"/>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="3"/>
+      <c r="H24" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -3127,93 +3117,93 @@
   <dimension ref="A1:R75"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="8" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="15" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="8" style="1" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="15" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="52"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="J1" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="K1" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="L1" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="M1" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="N1" s="5" t="s">
+      <c r="N1" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="O1" s="5" t="s">
+      <c r="O1" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="P1" s="5" t="s">
+      <c r="P1" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="Q1" s="5" t="s">
+      <c r="Q1" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="R1" s="5" t="s">
+      <c r="R1" s="6" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="6" t="n">
+    <row r="2" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="F2" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="G2" s="3" t="s">
         <v>48</v>
       </c>
       <c r="H2" s="8" t="n">
@@ -3245,34 +3235,34 @@
         <f aca="false">1+(O2*2.25)</f>
         <v>1.151875</v>
       </c>
-      <c r="Q2" s="6" t="n">
+      <c r="Q2" s="7" t="n">
         <f aca="false">ROUND(P2,0)</f>
         <v>1</v>
       </c>
-      <c r="R2" s="2" t="s">
+      <c r="R2" s="3" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="6" t="n">
+    <row r="3" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="G3" s="3" t="s">
         <v>48</v>
       </c>
       <c r="H3" s="8" t="n">
@@ -3304,34 +3294,34 @@
         <f aca="false">1+(O3*2.25)</f>
         <v>1.185625</v>
       </c>
-      <c r="Q3" s="6" t="n">
+      <c r="Q3" s="7" t="n">
         <f aca="false">ROUND(P3,0)</f>
         <v>1</v>
       </c>
-      <c r="R3" s="2" t="s">
+      <c r="R3" s="3" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="6" t="n">
+    <row r="4" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F4" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="G4" s="3" t="s">
         <v>48</v>
       </c>
       <c r="H4" s="8" t="n">
@@ -3363,34 +3353,34 @@
         <f aca="false">1+(O4*2.25)</f>
         <v>1.174375</v>
       </c>
-      <c r="Q4" s="6" t="n">
+      <c r="Q4" s="7" t="n">
         <f aca="false">ROUND(P4,0)</f>
         <v>1</v>
       </c>
-      <c r="R4" s="2" t="s">
+      <c r="R4" s="3" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="6" t="n">
+    <row r="5" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="F5" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="G5" s="7" t="s">
+      <c r="G5" s="3" t="s">
         <v>48</v>
       </c>
       <c r="H5" s="8" t="n">
@@ -3422,34 +3412,34 @@
         <f aca="false">1+(O5*2.25)</f>
         <v>1.12375</v>
       </c>
-      <c r="Q5" s="6" t="n">
+      <c r="Q5" s="7" t="n">
         <f aca="false">ROUND(P5,0)</f>
         <v>1</v>
       </c>
-      <c r="R5" s="2" t="s">
+      <c r="R5" s="3" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="6" t="n">
+    <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F6" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="G6" s="7" t="s">
+      <c r="F6" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G6" s="3" t="s">
         <v>48</v>
       </c>
       <c r="H6" s="8" t="n">
@@ -3481,34 +3471,34 @@
         <f aca="false">1+(O6*2.25)</f>
         <v>1.9</v>
       </c>
-      <c r="Q6" s="6" t="n">
+      <c r="Q6" s="7" t="n">
         <f aca="false">ROUND(P6,0)</f>
         <v>2</v>
       </c>
-      <c r="R6" s="2" t="s">
+      <c r="R6" s="3" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="6" t="n">
+    <row r="7" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F7" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="G7" s="7" t="s">
+      <c r="F7" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G7" s="3" t="s">
         <v>48</v>
       </c>
       <c r="H7" s="8" t="n">
@@ -3540,34 +3530,34 @@
         <f aca="false">1+(O7*2.25)</f>
         <v>1.984375</v>
       </c>
-      <c r="Q7" s="6" t="n">
+      <c r="Q7" s="7" t="n">
         <f aca="false">ROUND(P7,0)</f>
         <v>2</v>
       </c>
-      <c r="R7" s="2" t="s">
+      <c r="R7" s="3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="E8" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F8" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="G8" s="7" t="s">
+      <c r="F8" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G8" s="3" t="s">
         <v>48</v>
       </c>
       <c r="H8" s="8" t="n">
@@ -3599,34 +3589,34 @@
         <f aca="false">1+(O8*2.25)</f>
         <v>1.950625</v>
       </c>
-      <c r="Q8" s="6" t="n">
+      <c r="Q8" s="7" t="n">
         <f aca="false">ROUND(P8,0)</f>
         <v>2</v>
       </c>
-      <c r="R8" s="2" t="s">
+      <c r="R8" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C9" s="2" t="s">
+      <c r="D9" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="E9" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="E9" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="G9" s="7" t="s">
+      <c r="F9" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G9" s="3" t="s">
         <v>48</v>
       </c>
       <c r="H9" s="8" t="n">
@@ -3658,34 +3648,34 @@
         <f aca="false">1+(O9*2.25)</f>
         <v>1.815625</v>
       </c>
-      <c r="Q9" s="6" t="n">
+      <c r="Q9" s="7" t="n">
         <f aca="false">ROUND(P9,0)</f>
         <v>2</v>
       </c>
-      <c r="R9" s="2" t="s">
+      <c r="R9" s="3" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C10" s="2" t="s">
+      <c r="D10" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="E10" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="G10" s="7" t="s">
+      <c r="F10" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G10" s="3" t="s">
         <v>48</v>
       </c>
       <c r="H10" s="8" t="n">
@@ -3717,34 +3707,34 @@
         <f aca="false">1+(O10*2.25)</f>
         <v>1.815625</v>
       </c>
-      <c r="Q10" s="6" t="n">
+      <c r="Q10" s="7" t="n">
         <f aca="false">ROUND(P10,0)</f>
         <v>2</v>
       </c>
-      <c r="R10" s="2" t="s">
+      <c r="R10" s="3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C11" s="2" t="s">
+      <c r="D11" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="E11" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="E11" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="F11" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="G11" s="7" t="s">
+      <c r="F11" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G11" s="3" t="s">
         <v>48</v>
       </c>
       <c r="H11" s="8" t="n">
@@ -3776,34 +3766,34 @@
         <f aca="false">1+(O11*2.25)</f>
         <v>1.781875</v>
       </c>
-      <c r="Q11" s="6" t="n">
+      <c r="Q11" s="7" t="n">
         <f aca="false">ROUND(P11,0)</f>
         <v>2</v>
       </c>
-      <c r="R11" s="2" t="s">
+      <c r="R11" s="3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="D12" s="2" t="s">
+      <c r="D12" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E12" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="E12" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="F12" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="G12" s="7" t="s">
+      <c r="F12" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G12" s="3" t="s">
         <v>48</v>
       </c>
       <c r="H12" s="8" t="n">
@@ -3835,34 +3825,34 @@
         <f aca="false">1+(O12*2.25)</f>
         <v>1.860625</v>
       </c>
-      <c r="Q12" s="6" t="n">
+      <c r="Q12" s="7" t="n">
         <f aca="false">ROUND(P12,0)</f>
         <v>2</v>
       </c>
-      <c r="R12" s="2" t="s">
+      <c r="R12" s="3" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C13" s="2" t="s">
+      <c r="D13" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="E13" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="E13" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="F13" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="G13" s="7" t="s">
+      <c r="F13" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G13" s="3" t="s">
         <v>48</v>
       </c>
       <c r="H13" s="8" t="n">
@@ -3894,34 +3884,34 @@
         <f aca="false">1+(O13*2.25)</f>
         <v>1.838125</v>
       </c>
-      <c r="Q13" s="6" t="n">
+      <c r="Q13" s="7" t="n">
         <f aca="false">ROUND(P13,0)</f>
         <v>2</v>
       </c>
-      <c r="R13" s="2" t="s">
+      <c r="R13" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="D14" s="2" t="s">
+      <c r="D14" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="E14" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="F14" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="G14" s="7" t="s">
+      <c r="F14" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G14" s="3" t="s">
         <v>48</v>
       </c>
       <c r="H14" s="8" t="n">
@@ -3953,34 +3943,34 @@
         <f aca="false">1+(O14*2.25)</f>
         <v>1.855</v>
       </c>
-      <c r="Q14" s="6" t="n">
+      <c r="Q14" s="7" t="n">
         <f aca="false">ROUND(P14,0)</f>
         <v>2</v>
       </c>
-      <c r="R14" s="2" t="s">
+      <c r="R14" s="3" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="D15" s="2" t="s">
+      <c r="D15" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="E15" s="2" t="s">
+      <c r="E15" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="F15" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="G15" s="7" t="s">
+      <c r="F15" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G15" s="3" t="s">
         <v>48</v>
       </c>
       <c r="H15" s="8" t="n">
@@ -4012,34 +4002,34 @@
         <f aca="false">1+(O15*2.25)</f>
         <v>1.838125</v>
       </c>
-      <c r="Q15" s="6" t="n">
+      <c r="Q15" s="7" t="n">
         <f aca="false">ROUND(P15,0)</f>
         <v>2</v>
       </c>
-      <c r="R15" s="2" t="s">
+      <c r="R15" s="3" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C16" s="2" t="s">
+      <c r="D16" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="E16" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="E16" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="F16" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="G16" s="7" t="s">
+      <c r="F16" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G16" s="3" t="s">
         <v>48</v>
       </c>
       <c r="H16" s="8" t="n">
@@ -4071,34 +4061,34 @@
         <f aca="false">1+(O16*2.25)</f>
         <v>1.804375</v>
       </c>
-      <c r="Q16" s="6" t="n">
+      <c r="Q16" s="7" t="n">
         <f aca="false">ROUND(P16,0)</f>
         <v>2</v>
       </c>
-      <c r="R16" s="2" t="s">
+      <c r="R16" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C17" s="2" t="s">
+      <c r="D17" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="E17" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="E17" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="F17" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="G17" s="7" t="s">
+      <c r="F17" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G17" s="3" t="s">
         <v>48</v>
       </c>
       <c r="H17" s="8" t="n">
@@ -4130,34 +4120,34 @@
         <f aca="false">1+(O17*2.25)</f>
         <v>1.855</v>
       </c>
-      <c r="Q17" s="6" t="n">
+      <c r="Q17" s="7" t="n">
         <f aca="false">ROUND(P17,0)</f>
         <v>2</v>
       </c>
-      <c r="R17" s="2" t="s">
+      <c r="R17" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C18" s="3" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C18" s="2" t="s">
+      <c r="D18" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="E18" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="F18" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="G18" s="7" t="s">
+      <c r="F18" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G18" s="3" t="s">
         <v>48</v>
       </c>
       <c r="H18" s="8" t="n">
@@ -4189,34 +4179,34 @@
         <f aca="false">1+(O18*2.25)</f>
         <v>1.815625</v>
       </c>
-      <c r="Q18" s="6" t="n">
+      <c r="Q18" s="7" t="n">
         <f aca="false">ROUND(P18,0)</f>
         <v>2</v>
       </c>
-      <c r="R18" s="2" t="s">
+      <c r="R18" s="3" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C19" s="3" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C19" s="2" t="s">
+      <c r="D19" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="E19" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="E19" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="F19" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="G19" s="7" t="s">
+      <c r="F19" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G19" s="3" t="s">
         <v>48</v>
       </c>
       <c r="H19" s="8" t="n">
@@ -4248,34 +4238,34 @@
         <f aca="false">1+(O19*2.25)</f>
         <v>2.71</v>
       </c>
-      <c r="Q19" s="6" t="n">
+      <c r="Q19" s="7" t="n">
         <f aca="false">ROUND(P19,0)</f>
         <v>3</v>
       </c>
-      <c r="R19" s="2" t="s">
+      <c r="R19" s="3" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C20" s="2" t="s">
+      <c r="D20" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="D20" s="2" t="s">
+      <c r="E20" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="E20" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="F20" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="G20" s="7" t="s">
+      <c r="F20" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G20" s="3" t="s">
         <v>48</v>
       </c>
       <c r="H20" s="8" t="n">
@@ -4307,34 +4297,34 @@
         <f aca="false">1+(O20*2.25)</f>
         <v>2.726875</v>
       </c>
-      <c r="Q20" s="6" t="n">
+      <c r="Q20" s="7" t="n">
         <f aca="false">ROUND(P20,0)</f>
         <v>3</v>
       </c>
-      <c r="R20" s="2" t="s">
+      <c r="R20" s="3" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C21" s="3" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C21" s="2" t="s">
+      <c r="D21" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="D21" s="2" t="s">
+      <c r="E21" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="E21" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="F21" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="G21" s="7" t="s">
+      <c r="F21" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G21" s="3" t="s">
         <v>48</v>
       </c>
       <c r="H21" s="8" t="n">
@@ -4366,34 +4356,34 @@
         <f aca="false">1+(O21*2.25)</f>
         <v>2.71</v>
       </c>
-      <c r="Q21" s="6" t="n">
+      <c r="Q21" s="7" t="n">
         <f aca="false">ROUND(P21,0)</f>
         <v>3</v>
       </c>
-      <c r="R21" s="2" t="s">
+      <c r="R21" s="3" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C22" s="3" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C22" s="2" t="s">
+      <c r="D22" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="E22" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="E22" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="F22" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="G22" s="7" t="s">
+      <c r="F22" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G22" s="3" t="s">
         <v>48</v>
       </c>
       <c r="H22" s="8" t="n">
@@ -4425,34 +4415,34 @@
         <f aca="false">1+(O22*2.25)</f>
         <v>2.755</v>
       </c>
-      <c r="Q22" s="6" t="n">
+      <c r="Q22" s="7" t="n">
         <f aca="false">ROUND(P22,0)</f>
         <v>3</v>
       </c>
-      <c r="R22" s="2" t="s">
+      <c r="R22" s="3" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C23" s="3" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C23" s="2" t="s">
+      <c r="D23" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="D23" s="2" t="s">
+      <c r="E23" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="E23" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="F23" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="G23" s="7" t="s">
+      <c r="F23" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G23" s="3" t="s">
         <v>48</v>
       </c>
       <c r="H23" s="8" t="n">
@@ -4484,34 +4474,34 @@
         <f aca="false">1+(O23*2.25)</f>
         <v>2.693125</v>
       </c>
-      <c r="Q23" s="6" t="n">
+      <c r="Q23" s="7" t="n">
         <f aca="false">ROUND(P23,0)</f>
         <v>3</v>
       </c>
-      <c r="R23" s="2" t="s">
+      <c r="R23" s="3" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C24" s="3" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="D24" s="2" t="s">
+      <c r="D24" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="E24" s="2" t="s">
+      <c r="E24" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="F24" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="G24" s="7" t="s">
+      <c r="F24" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G24" s="3" t="s">
         <v>48</v>
       </c>
       <c r="H24" s="8" t="n">
@@ -4543,34 +4533,34 @@
         <f aca="false">1+(O24*2.25)</f>
         <v>2.7325</v>
       </c>
-      <c r="Q24" s="6" t="n">
+      <c r="Q24" s="7" t="n">
         <f aca="false">ROUND(P24,0)</f>
         <v>3</v>
       </c>
-      <c r="R24" s="2" t="s">
+      <c r="R24" s="3" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C25" s="3" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="D25" s="2" t="s">
+      <c r="D25" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="E25" s="2" t="s">
+      <c r="E25" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="F25" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="G25" s="7" t="s">
+      <c r="F25" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G25" s="3" t="s">
         <v>48</v>
       </c>
       <c r="H25" s="8" t="n">
@@ -4602,34 +4592,34 @@
         <f aca="false">1+(O25*2.25)</f>
         <v>2.7775</v>
       </c>
-      <c r="Q25" s="6" t="n">
+      <c r="Q25" s="7" t="n">
         <f aca="false">ROUND(P25,0)</f>
         <v>3</v>
       </c>
-      <c r="R25" s="2" t="s">
+      <c r="R25" s="3" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C26" s="3" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="F26" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="G26" s="7" t="s">
+      <c r="D26" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G26" s="3" t="s">
         <v>48</v>
       </c>
       <c r="H26" s="8" t="n">
@@ -4661,34 +4651,34 @@
         <f aca="false">1+(O26*2.25)</f>
         <v>2.771875</v>
       </c>
-      <c r="Q26" s="6" t="n">
+      <c r="Q26" s="7" t="n">
         <f aca="false">ROUND(P26,0)</f>
         <v>3</v>
       </c>
-      <c r="R26" s="2" t="s">
+      <c r="R26" s="3" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C27" s="3" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C27" s="2" t="s">
+      <c r="D27" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="D27" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="F27" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="G27" s="7" t="s">
+      <c r="E27" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G27" s="3" t="s">
         <v>48</v>
       </c>
       <c r="H27" s="8" t="n">
@@ -4720,34 +4710,34 @@
         <f aca="false">1+(O27*2.25)</f>
         <v>2.67625</v>
       </c>
-      <c r="Q27" s="6" t="n">
+      <c r="Q27" s="7" t="n">
         <f aca="false">ROUND(P27,0)</f>
         <v>3</v>
       </c>
-      <c r="R27" s="2" t="s">
+      <c r="R27" s="3" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C28" s="3" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="F28" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="G28" s="7" t="s">
+      <c r="D28" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G28" s="3" t="s">
         <v>48</v>
       </c>
       <c r="H28" s="8" t="n">
@@ -4779,34 +4769,34 @@
         <f aca="false">1+(O28*2.25)</f>
         <v>2.771875</v>
       </c>
-      <c r="Q28" s="6" t="n">
+      <c r="Q28" s="7" t="n">
         <f aca="false">ROUND(P28,0)</f>
         <v>3</v>
       </c>
-      <c r="R28" s="2" t="s">
+      <c r="R28" s="3" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C29" s="3" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="29" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C29" s="2" t="s">
+      <c r="D29" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="E29" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="D29" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="F29" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="G29" s="7" t="s">
+      <c r="F29" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G29" s="3" t="s">
         <v>48</v>
       </c>
       <c r="H29" s="8" t="n">
@@ -4838,34 +4828,34 @@
         <f aca="false">1+(O29*2.25)</f>
         <v>2.72125</v>
       </c>
-      <c r="Q29" s="6" t="n">
+      <c r="Q29" s="7" t="n">
         <f aca="false">ROUND(P29,0)</f>
         <v>3</v>
       </c>
-      <c r="R29" s="2" t="s">
+      <c r="R29" s="3" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C30" s="3" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="30" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="D30" s="2" t="s">
+      <c r="D30" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E30" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="E30" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="F30" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="G30" s="7" t="s">
+      <c r="F30" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G30" s="3" t="s">
         <v>48</v>
       </c>
       <c r="H30" s="8" t="n">
@@ -4897,34 +4887,34 @@
         <f aca="false">1+(O30*2.25)</f>
         <v>2.760625</v>
       </c>
-      <c r="Q30" s="6" t="n">
+      <c r="Q30" s="7" t="n">
         <f aca="false">ROUND(P30,0)</f>
         <v>3</v>
       </c>
-      <c r="R30" s="2" t="s">
+      <c r="R30" s="3" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C31" s="3" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="31" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="D31" s="2" t="s">
+      <c r="D31" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E31" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="E31" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="F31" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="G31" s="7" t="s">
+      <c r="F31" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G31" s="3" t="s">
         <v>48</v>
       </c>
       <c r="H31" s="8" t="n">
@@ -4956,34 +4946,34 @@
         <f aca="false">1+(O31*2.25)</f>
         <v>2.805625</v>
       </c>
-      <c r="Q31" s="6" t="n">
+      <c r="Q31" s="7" t="n">
         <f aca="false">ROUND(P31,0)</f>
         <v>3</v>
       </c>
-      <c r="R31" s="2" t="s">
+      <c r="R31" s="3" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C32" s="3" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C32" s="2" t="s">
+      <c r="D32" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="D32" s="2" t="s">
+      <c r="E32" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="E32" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="F32" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="G32" s="7" t="s">
+      <c r="F32" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G32" s="3" t="s">
         <v>48</v>
       </c>
       <c r="H32" s="8" t="n">
@@ -5015,34 +5005,34 @@
         <f aca="false">1+(O32*2.25)</f>
         <v>2.693125</v>
       </c>
-      <c r="Q32" s="6" t="n">
+      <c r="Q32" s="7" t="n">
         <f aca="false">ROUND(P32,0)</f>
         <v>3</v>
       </c>
-      <c r="R32" s="2" t="s">
+      <c r="R32" s="3" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C33" s="3" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C33" s="2" t="s">
+      <c r="D33" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="E33" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="D33" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="F33" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="G33" s="7" t="s">
+      <c r="F33" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G33" s="3" t="s">
         <v>48</v>
       </c>
       <c r="H33" s="8" t="n">
@@ -5074,34 +5064,34 @@
         <f aca="false">1+(O33*2.25)</f>
         <v>2.76625</v>
       </c>
-      <c r="Q33" s="6" t="n">
+      <c r="Q33" s="7" t="n">
         <f aca="false">ROUND(P33,0)</f>
         <v>3</v>
       </c>
-      <c r="R33" s="2" t="s">
+      <c r="R33" s="3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C34" s="3" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C34" s="2" t="s">
+      <c r="D34" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="E34" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="D34" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="F34" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="G34" s="7" t="s">
+      <c r="F34" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G34" s="3" t="s">
         <v>60</v>
       </c>
       <c r="H34" s="8" t="n">
@@ -5133,34 +5123,34 @@
         <f aca="false">1+(O34*2.25)</f>
         <v>3.79</v>
       </c>
-      <c r="Q34" s="6" t="n">
+      <c r="Q34" s="7" t="n">
         <f aca="false">ROUND(P34,0)</f>
         <v>4</v>
       </c>
-      <c r="R34" s="2" t="s">
+      <c r="R34" s="3" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C35" s="3" t="s">
         <v>147</v>
       </c>
-    </row>
-    <row r="35" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C35" s="2" t="s">
+      <c r="D35" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="E35" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="D35" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="F35" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="G35" s="7" t="s">
+      <c r="F35" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G35" s="3" t="s">
         <v>48</v>
       </c>
       <c r="H35" s="8" t="n">
@@ -5192,34 +5182,34 @@
         <f aca="false">1+(O35*2.25)</f>
         <v>3.68875</v>
       </c>
-      <c r="Q35" s="6" t="n">
+      <c r="Q35" s="7" t="n">
         <f aca="false">ROUND(P35,0)</f>
         <v>4</v>
       </c>
-      <c r="R35" s="2" t="s">
+      <c r="R35" s="3" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C36" s="3" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="36" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="F36" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="G36" s="7" t="s">
+      <c r="D36" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G36" s="3" t="s">
         <v>48</v>
       </c>
       <c r="H36" s="8" t="n">
@@ -5251,34 +5241,34 @@
         <f aca="false">1+(O36*2.25)</f>
         <v>3.7675</v>
       </c>
-      <c r="Q36" s="6" t="n">
+      <c r="Q36" s="7" t="n">
         <f aca="false">ROUND(P36,0)</f>
         <v>4</v>
       </c>
-      <c r="R36" s="2" t="s">
+      <c r="R36" s="3" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C37" s="3" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="37" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C37" s="2" t="s">
+      <c r="D37" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="D37" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="F37" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="G37" s="7" t="s">
+      <c r="E37" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G37" s="3" t="s">
         <v>60</v>
       </c>
       <c r="H37" s="8" t="n">
@@ -5310,34 +5300,34 @@
         <f aca="false">1+(O37*2.25)</f>
         <v>3.835</v>
       </c>
-      <c r="Q37" s="6" t="n">
+      <c r="Q37" s="7" t="n">
         <f aca="false">ROUND(P37,0)</f>
         <v>4</v>
       </c>
-      <c r="R37" s="2" t="s">
+      <c r="R37" s="3" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C38" s="3" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="38" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C38" s="2" t="s">
+      <c r="D38" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="E38" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="D38" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="F38" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="G38" s="7" t="s">
+      <c r="F38" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G38" s="3" t="s">
         <v>60</v>
       </c>
       <c r="H38" s="8" t="n">
@@ -5369,34 +5359,34 @@
         <f aca="false">1+(O38*2.25)</f>
         <v>3.761875</v>
       </c>
-      <c r="Q38" s="6" t="n">
+      <c r="Q38" s="7" t="n">
         <f aca="false">ROUND(P38,0)</f>
         <v>4</v>
       </c>
-      <c r="R38" s="2" t="s">
+      <c r="R38" s="3" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C39" s="3" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="39" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C39" s="2" t="s">
+      <c r="D39" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="D39" s="2" t="s">
+      <c r="E39" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="E39" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="F39" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="G39" s="7" t="s">
+      <c r="F39" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G39" s="3" t="s">
         <v>48</v>
       </c>
       <c r="H39" s="8" t="n">
@@ -5428,34 +5418,34 @@
         <f aca="false">1+(O39*2.25)</f>
         <v>3.80125</v>
       </c>
-      <c r="Q39" s="6" t="n">
+      <c r="Q39" s="7" t="n">
         <f aca="false">ROUND(P39,0)</f>
         <v>4</v>
       </c>
-      <c r="R39" s="2" t="s">
+      <c r="R39" s="3" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C40" s="3" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="40" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C40" s="2" t="s">
+      <c r="D40" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="E40" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="D40" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="F40" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="G40" s="7" t="s">
+      <c r="F40" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G40" s="3" t="s">
         <v>48</v>
       </c>
       <c r="H40" s="8" t="n">
@@ -5487,34 +5477,34 @@
         <f aca="false">1+(O40*2.25)</f>
         <v>3.818125</v>
       </c>
-      <c r="Q40" s="6" t="n">
+      <c r="Q40" s="7" t="n">
         <f aca="false">ROUND(P40,0)</f>
         <v>4</v>
       </c>
-      <c r="R40" s="2" t="s">
+      <c r="R40" s="3" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C41" s="3" t="s">
         <v>165</v>
       </c>
-    </row>
-    <row r="41" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="D41" s="2" t="s">
+      <c r="D41" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E41" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="E41" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="F41" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="G41" s="7" t="s">
+      <c r="F41" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G41" s="3" t="s">
         <v>60</v>
       </c>
       <c r="H41" s="8" t="n">
@@ -5546,34 +5536,34 @@
         <f aca="false">1+(O41*2.25)</f>
         <v>3.806875</v>
       </c>
-      <c r="Q41" s="6" t="n">
+      <c r="Q41" s="7" t="n">
         <f aca="false">ROUND(P41,0)</f>
         <v>4</v>
       </c>
-      <c r="R41" s="2" t="s">
+      <c r="R41" s="3" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C42" s="3" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="42" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="D42" s="2" t="s">
+      <c r="D42" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E42" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="E42" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="F42" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="G42" s="7" t="s">
+      <c r="F42" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G42" s="3" t="s">
         <v>60</v>
       </c>
       <c r="H42" s="8" t="n">
@@ -5605,34 +5595,34 @@
         <f aca="false">1+(O42*2.25)</f>
         <v>3.795625</v>
       </c>
-      <c r="Q42" s="6" t="n">
+      <c r="Q42" s="7" t="n">
         <f aca="false">ROUND(P42,0)</f>
         <v>4</v>
       </c>
-      <c r="R42" s="2" t="s">
+      <c r="R42" s="3" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C43" s="3" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="43" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="F43" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="G43" s="7" t="s">
+      <c r="D43" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G43" s="3" t="s">
         <v>48</v>
       </c>
       <c r="H43" s="8" t="n">
@@ -5664,34 +5654,34 @@
         <f aca="false">1+(O43*2.25)</f>
         <v>3.82375</v>
       </c>
-      <c r="Q43" s="6" t="n">
+      <c r="Q43" s="7" t="n">
         <f aca="false">ROUND(P43,0)</f>
         <v>4</v>
       </c>
-      <c r="R43" s="2" t="s">
+      <c r="R43" s="3" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C44" s="3" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="44" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C44" s="2" t="s">
+      <c r="D44" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="D44" s="2" t="s">
+      <c r="E44" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="E44" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="F44" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="G44" s="7" t="s">
+      <c r="F44" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G44" s="3" t="s">
         <v>60</v>
       </c>
       <c r="H44" s="8" t="n">
@@ -5723,34 +5713,34 @@
         <f aca="false">1+(O44*2.25)</f>
         <v>3.68875</v>
       </c>
-      <c r="Q44" s="6" t="n">
+      <c r="Q44" s="7" t="n">
         <f aca="false">ROUND(P44,0)</f>
         <v>4</v>
       </c>
-      <c r="R44" s="2" t="s">
+      <c r="R44" s="3" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C45" s="3" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="45" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="F45" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="G45" s="7" t="s">
+      <c r="D45" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G45" s="3" t="s">
         <v>48</v>
       </c>
       <c r="H45" s="8" t="n">
@@ -5782,34 +5772,34 @@
         <f aca="false">1+(O45*2.25)</f>
         <v>3.806875</v>
       </c>
-      <c r="Q45" s="6" t="n">
+      <c r="Q45" s="7" t="n">
         <f aca="false">ROUND(P45,0)</f>
         <v>4</v>
       </c>
-      <c r="R45" s="2" t="s">
+      <c r="R45" s="3" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C46" s="3" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="46" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C46" s="2" t="s">
+      <c r="D46" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="D46" s="2" t="s">
+      <c r="E46" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="E46" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="F46" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="G46" s="7" t="s">
+      <c r="F46" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G46" s="3" t="s">
         <v>48</v>
       </c>
       <c r="H46" s="8" t="n">
@@ -5841,34 +5831,34 @@
         <f aca="false">1+(O46*2.25)</f>
         <v>3.671875</v>
       </c>
-      <c r="Q46" s="6" t="n">
+      <c r="Q46" s="7" t="n">
         <f aca="false">ROUND(P46,0)</f>
         <v>4</v>
       </c>
-      <c r="R46" s="2" t="s">
+      <c r="R46" s="3" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C47" s="3" t="s">
         <v>181</v>
       </c>
-    </row>
-    <row r="47" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="D47" s="2" t="s">
+      <c r="D47" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="E47" s="2" t="s">
+      <c r="E47" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="F47" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="G47" s="7" t="s">
+      <c r="F47" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G47" s="3" t="s">
         <v>48</v>
       </c>
       <c r="H47" s="8" t="n">
@@ -5900,34 +5890,34 @@
         <f aca="false">1+(O47*2.25)</f>
         <v>3.784375</v>
       </c>
-      <c r="Q47" s="6" t="n">
+      <c r="Q47" s="7" t="n">
         <f aca="false">ROUND(P47,0)</f>
         <v>4</v>
       </c>
-      <c r="R47" s="2" t="s">
+      <c r="R47" s="3" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C48" s="3" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="48" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C48" s="2" t="s">
+      <c r="D48" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="E48" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="D48" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="F48" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="G48" s="7" t="s">
+      <c r="F48" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G48" s="3" t="s">
         <v>60</v>
       </c>
       <c r="H48" s="8" t="n">
@@ -5959,34 +5949,34 @@
         <f aca="false">1+(O48*2.25)</f>
         <v>3.784375</v>
       </c>
-      <c r="Q48" s="6" t="n">
+      <c r="Q48" s="7" t="n">
         <f aca="false">ROUND(P48,0)</f>
         <v>4</v>
       </c>
-      <c r="R48" s="2" t="s">
+      <c r="R48" s="3" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C49" s="3" t="s">
         <v>186</v>
       </c>
-    </row>
-    <row r="49" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C49" s="2" t="s">
+      <c r="D49" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="E49" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="D49" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="E49" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="F49" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="G49" s="7" t="s">
+      <c r="F49" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G49" s="3" t="s">
         <v>48</v>
       </c>
       <c r="H49" s="8" t="n">
@@ -6018,34 +6008,34 @@
         <f aca="false">1+(O49*2.25)</f>
         <v>3.68875</v>
       </c>
-      <c r="Q49" s="6" t="n">
+      <c r="Q49" s="7" t="n">
         <f aca="false">ROUND(P49,0)</f>
         <v>4</v>
       </c>
-      <c r="R49" s="2" t="s">
+      <c r="R49" s="3" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C50" s="3" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="50" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C50" s="2" t="s">
+      <c r="D50" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="E50" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="D50" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="F50" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="G50" s="7" t="s">
+      <c r="F50" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G50" s="3" t="s">
         <v>48</v>
       </c>
       <c r="H50" s="8" t="n">
@@ -6077,34 +6067,34 @@
         <f aca="false">1+(O50*2.25)</f>
         <v>3.79</v>
       </c>
-      <c r="Q50" s="6" t="n">
+      <c r="Q50" s="7" t="n">
         <f aca="false">ROUND(P50,0)</f>
         <v>4</v>
       </c>
-      <c r="R50" s="2" t="s">
+      <c r="R50" s="3" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C51" s="3" t="s">
         <v>192</v>
       </c>
-    </row>
-    <row r="51" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="D51" s="2" t="s">
+      <c r="D51" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="E51" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="E51" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="F51" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="G51" s="7" t="s">
+      <c r="F51" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G51" s="3" t="s">
         <v>60</v>
       </c>
       <c r="H51" s="8" t="n">
@@ -6136,34 +6126,34 @@
         <f aca="false">1+(O51*2.25)</f>
         <v>3.806875</v>
       </c>
-      <c r="Q51" s="6" t="n">
+      <c r="Q51" s="7" t="n">
         <f aca="false">ROUND(P51,0)</f>
         <v>4</v>
       </c>
-      <c r="R51" s="2" t="s">
+      <c r="R51" s="3" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C52" s="3" t="s">
         <v>194</v>
       </c>
-    </row>
-    <row r="52" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C52" s="2" t="s">
+      <c r="D52" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="D52" s="2" t="s">
+      <c r="E52" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="E52" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="F52" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="G52" s="7" t="s">
+      <c r="F52" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G52" s="3" t="s">
         <v>48</v>
       </c>
       <c r="H52" s="8" t="n">
@@ -6195,34 +6185,34 @@
         <f aca="false">1+(O52*2.25)</f>
         <v>3.773125</v>
       </c>
-      <c r="Q52" s="6" t="n">
+      <c r="Q52" s="7" t="n">
         <f aca="false">ROUND(P52,0)</f>
         <v>4</v>
       </c>
-      <c r="R52" s="2" t="s">
+      <c r="R52" s="3" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C53" s="3" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="53" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="D53" s="2" t="s">
+      <c r="D53" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="E53" s="2" t="s">
+      <c r="E53" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="F53" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="G53" s="7" t="s">
+      <c r="F53" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G53" s="3" t="s">
         <v>60</v>
       </c>
       <c r="H53" s="8" t="n">
@@ -6254,34 +6244,34 @@
         <f aca="false">1+(O53*2.25)</f>
         <v>3.784375</v>
       </c>
-      <c r="Q53" s="6" t="n">
+      <c r="Q53" s="7" t="n">
         <f aca="false">ROUND(P53,0)</f>
         <v>4</v>
       </c>
-      <c r="R53" s="2" t="s">
+      <c r="R53" s="3" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C54" s="3" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="54" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B54" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C54" s="2" t="s">
+      <c r="D54" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="E54" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="D54" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="E54" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="F54" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="G54" s="7" t="s">
+      <c r="F54" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G54" s="3" t="s">
         <v>60</v>
       </c>
       <c r="H54" s="8" t="n">
@@ -6313,34 +6303,34 @@
         <f aca="false">1+(O54*2.25)</f>
         <v>4.87</v>
       </c>
-      <c r="Q54" s="6" t="n">
+      <c r="Q54" s="7" t="n">
         <f aca="false">ROUND(P54,0)</f>
         <v>5</v>
       </c>
-      <c r="R54" s="2" t="s">
+      <c r="R54" s="3" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C55" s="3" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="55" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B55" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C55" s="2" t="s">
+      <c r="D55" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="E55" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="D55" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="E55" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="F55" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="G55" s="7" t="s">
+      <c r="F55" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G55" s="3" t="s">
         <v>60</v>
       </c>
       <c r="H55" s="8" t="n">
@@ -6372,34 +6362,34 @@
         <f aca="false">1+(O55*2.25)</f>
         <v>4.825</v>
       </c>
-      <c r="Q55" s="6" t="n">
+      <c r="Q55" s="7" t="n">
         <f aca="false">ROUND(P55,0)</f>
         <v>5</v>
       </c>
-      <c r="R55" s="2" t="s">
+      <c r="R55" s="3" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C56" s="3" t="s">
         <v>206</v>
       </c>
-    </row>
-    <row r="56" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B56" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="E56" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="F56" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="G56" s="7" t="s">
+      <c r="D56" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="F56" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G56" s="3" t="s">
         <v>60</v>
       </c>
       <c r="H56" s="8" t="n">
@@ -6431,34 +6421,34 @@
         <f aca="false">1+(O56*2.25)</f>
         <v>4.898125</v>
       </c>
-      <c r="Q56" s="6" t="n">
+      <c r="Q56" s="7" t="n">
         <f aca="false">ROUND(P56,0)</f>
         <v>5</v>
       </c>
-      <c r="R56" s="2" t="s">
+      <c r="R56" s="3" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C57" s="3" t="s">
         <v>208</v>
       </c>
-    </row>
-    <row r="57" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C57" s="2" t="s">
+      <c r="D57" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="D57" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="E57" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="F57" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="G57" s="7" t="s">
+      <c r="E57" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G57" s="3" t="s">
         <v>60</v>
       </c>
       <c r="H57" s="8" t="n">
@@ -6490,34 +6480,34 @@
         <f aca="false">1+(O57*2.25)</f>
         <v>4.909375</v>
       </c>
-      <c r="Q57" s="6" t="n">
+      <c r="Q57" s="7" t="n">
         <f aca="false">ROUND(P57,0)</f>
         <v>5</v>
       </c>
-      <c r="R57" s="2" t="s">
+      <c r="R57" s="3" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C58" s="3" t="s">
         <v>211</v>
       </c>
-    </row>
-    <row r="58" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B58" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="E58" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="F58" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="G58" s="7" t="s">
+      <c r="D58" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G58" s="3" t="s">
         <v>60</v>
       </c>
       <c r="H58" s="8" t="n">
@@ -6549,34 +6539,34 @@
         <f aca="false">1+(O58*2.25)</f>
         <v>4.886875</v>
       </c>
-      <c r="Q58" s="6" t="n">
+      <c r="Q58" s="7" t="n">
         <f aca="false">ROUND(P58,0)</f>
         <v>5</v>
       </c>
-      <c r="R58" s="2" t="s">
+      <c r="R58" s="3" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A59" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C59" s="3" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="59" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B59" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="E59" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="F59" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="G59" s="7" t="s">
+      <c r="D59" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G59" s="3" t="s">
         <v>60</v>
       </c>
       <c r="H59" s="8" t="n">
@@ -6608,34 +6598,34 @@
         <f aca="false">1+(O59*2.25)</f>
         <v>4.88125</v>
       </c>
-      <c r="Q59" s="6" t="n">
+      <c r="Q59" s="7" t="n">
         <f aca="false">ROUND(P59,0)</f>
         <v>5</v>
       </c>
-      <c r="R59" s="2" t="s">
+      <c r="R59" s="3" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C60" s="3" t="s">
         <v>215</v>
       </c>
-    </row>
-    <row r="60" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B60" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C60" s="2" t="s">
+      <c r="D60" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="D60" s="2" t="s">
+      <c r="E60" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="E60" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="F60" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="G60" s="7" t="s">
+      <c r="F60" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G60" s="3" t="s">
         <v>60</v>
       </c>
       <c r="H60" s="8" t="n">
@@ -6667,34 +6657,34 @@
         <f aca="false">1+(O60*2.25)</f>
         <v>4.94875</v>
       </c>
-      <c r="Q60" s="6" t="n">
+      <c r="Q60" s="7" t="n">
         <f aca="false">ROUND(P60,0)</f>
         <v>5</v>
       </c>
-      <c r="R60" s="2" t="s">
+      <c r="R60" s="3" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A61" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C61" s="3" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="61" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B61" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C61" s="2" t="s">
+      <c r="D61" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="E61" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="D61" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="E61" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="F61" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="G61" s="7" t="s">
+      <c r="F61" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G61" s="3" t="s">
         <v>60</v>
       </c>
       <c r="H61" s="8" t="n">
@@ -6726,34 +6716,34 @@
         <f aca="false">1+(O61*2.25)</f>
         <v>4.87</v>
       </c>
-      <c r="Q61" s="6" t="n">
+      <c r="Q61" s="7" t="n">
         <f aca="false">ROUND(P61,0)</f>
         <v>5</v>
       </c>
-      <c r="R61" s="2" t="s">
+      <c r="R61" s="3" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A62" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C62" s="3" t="s">
         <v>222</v>
       </c>
-    </row>
-    <row r="62" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B62" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C62" s="2" t="s">
+      <c r="D62" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="E62" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="D62" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="E62" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="F62" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="G62" s="7" t="s">
+      <c r="F62" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G62" s="3" t="s">
         <v>60</v>
       </c>
       <c r="H62" s="8" t="n">
@@ -6785,34 +6775,34 @@
         <f aca="false">1+(O62*2.25)</f>
         <v>4.87</v>
       </c>
-      <c r="Q62" s="6" t="n">
+      <c r="Q62" s="7" t="n">
         <f aca="false">ROUND(P62,0)</f>
         <v>5</v>
       </c>
-      <c r="R62" s="2" t="s">
+      <c r="R62" s="3" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A63" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C63" s="3" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="63" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="B63" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C63" s="2" t="s">
+      <c r="D63" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="E63" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="D63" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="E63" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="F63" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="G63" s="7" t="s">
+      <c r="F63" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G63" s="3" t="s">
         <v>60</v>
       </c>
       <c r="H63" s="8" t="n">
@@ -6844,34 +6834,34 @@
         <f aca="false">1+(O63*2.25)</f>
         <v>6.04</v>
       </c>
-      <c r="Q63" s="6" t="n">
+      <c r="Q63" s="7" t="n">
         <f aca="false">ROUND(P63,0)</f>
         <v>6</v>
       </c>
-      <c r="R63" s="2" t="s">
+      <c r="R63" s="3" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A64" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C64" s="3" t="s">
         <v>228</v>
       </c>
-    </row>
-    <row r="64" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="B64" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C64" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="D64" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="E64" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="F64" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="G64" s="7" t="s">
+      <c r="D64" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="E64" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F64" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G64" s="3" t="s">
         <v>60</v>
       </c>
       <c r="H64" s="8" t="n">
@@ -6903,34 +6893,34 @@
         <f aca="false">1+(O64*2.25)</f>
         <v>6.0625</v>
       </c>
-      <c r="Q64" s="6" t="n">
+      <c r="Q64" s="7" t="n">
         <f aca="false">ROUND(P64,0)</f>
         <v>6</v>
       </c>
-      <c r="R64" s="2" t="s">
+      <c r="R64" s="3" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A65" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C65" s="3" t="s">
         <v>230</v>
       </c>
-    </row>
-    <row r="65" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="B65" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C65" s="2" t="s">
+      <c r="D65" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="D65" s="2" t="s">
+      <c r="E65" s="3" t="s">
         <v>232</v>
       </c>
-      <c r="E65" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="F65" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="G65" s="7" t="s">
+      <c r="F65" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G65" s="3" t="s">
         <v>60</v>
       </c>
       <c r="H65" s="8" t="n">
@@ -6962,34 +6952,34 @@
         <f aca="false">1+(O65*2.25)</f>
         <v>5.96125</v>
       </c>
-      <c r="Q65" s="6" t="n">
+      <c r="Q65" s="7" t="n">
         <f aca="false">ROUND(P65,0)</f>
         <v>6</v>
       </c>
-      <c r="R65" s="2" t="s">
+      <c r="R65" s="3" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A66" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C66" s="3" t="s">
         <v>234</v>
       </c>
-    </row>
-    <row r="66" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="B66" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C66" s="2" t="s">
+      <c r="D66" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="E66" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="D66" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="E66" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="F66" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="G66" s="7" t="s">
+      <c r="F66" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G66" s="3" t="s">
         <v>60</v>
       </c>
       <c r="H66" s="8" t="n">
@@ -7021,34 +7011,34 @@
         <f aca="false">1+(O66*2.25)</f>
         <v>6.056875</v>
       </c>
-      <c r="Q66" s="6" t="n">
+      <c r="Q66" s="7" t="n">
         <f aca="false">ROUND(P66,0)</f>
         <v>6</v>
       </c>
-      <c r="R66" s="2" t="s">
+      <c r="R66" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A67" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C67" s="3" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="67" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="B67" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C67" s="2" t="s">
+      <c r="D67" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="D67" s="2" t="s">
+      <c r="E67" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="E67" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="F67" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="G67" s="7" t="s">
+      <c r="F67" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G67" s="3" t="s">
         <v>60</v>
       </c>
       <c r="H67" s="8" t="n">
@@ -7080,34 +7070,34 @@
         <f aca="false">1+(O67*2.25)</f>
         <v>6.101875</v>
       </c>
-      <c r="Q67" s="6" t="n">
+      <c r="Q67" s="7" t="n">
         <f aca="false">ROUND(P67,0)</f>
         <v>6</v>
       </c>
-      <c r="R67" s="2" t="s">
+      <c r="R67" s="3" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A68" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C68" s="3" t="s">
         <v>241</v>
       </c>
-    </row>
-    <row r="68" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="B68" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C68" s="2" t="s">
+      <c r="D68" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="D68" s="2" t="s">
+      <c r="E68" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="E68" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="F68" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="G68" s="7" t="s">
+      <c r="F68" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G68" s="3" t="s">
         <v>60</v>
       </c>
       <c r="H68" s="8" t="n">
@@ -7139,35 +7129,35 @@
         <f aca="false">1+(O68*2.25)</f>
         <v>7.31125</v>
       </c>
-      <c r="Q68" s="6" t="n">
+      <c r="Q68" s="7" t="n">
         <f aca="false">ROUND(P68,0)</f>
         <v>7</v>
       </c>
-      <c r="R68" s="2" t="s">
+      <c r="R68" s="3" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A69" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C69" s="3" t="s">
         <v>245</v>
       </c>
-    </row>
-    <row r="69" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="B69" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C69" s="2" t="s">
+      <c r="D69" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="E69" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="D69" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="E69" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="F69" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="G69" s="7" t="s">
-        <v>248</v>
+      <c r="F69" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G69" s="3" t="s">
+        <v>60</v>
       </c>
       <c r="H69" s="8" t="n">
         <v>3.2</v>
@@ -7198,35 +7188,35 @@
         <f aca="false">1+(O69*2.25)</f>
         <v>8.430625</v>
       </c>
-      <c r="Q69" s="6" t="n">
+      <c r="Q69" s="7" t="n">
         <f aca="false">ROUND(P69,0)</f>
         <v>8</v>
       </c>
-      <c r="R69" s="2" t="s">
+      <c r="R69" s="3" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A70" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="E70" s="3" t="s">
         <v>249</v>
       </c>
-    </row>
-    <row r="70" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="B70" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C70" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="D70" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="E70" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="F70" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="G70" s="7" t="s">
-        <v>248</v>
+      <c r="F70" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G70" s="3" t="s">
+        <v>60</v>
       </c>
       <c r="H70" s="8" t="n">
         <v>3.5</v>
@@ -7257,35 +7247,35 @@
         <f aca="false">1+(O70*2.25)</f>
         <v>8.396875</v>
       </c>
-      <c r="Q70" s="6" t="n">
+      <c r="Q70" s="7" t="n">
         <f aca="false">ROUND(P70,0)</f>
         <v>8</v>
       </c>
-      <c r="R70" s="2" t="s">
+      <c r="R70" s="3" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A71" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D71" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="E71" s="3" t="s">
         <v>252</v>
       </c>
-    </row>
-    <row r="71" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="B71" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C71" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="D71" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="E71" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="F71" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="G71" s="7" t="s">
-        <v>248</v>
+      <c r="F71" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G71" s="3" t="s">
+        <v>60</v>
       </c>
       <c r="H71" s="8" t="n">
         <v>3.2</v>
@@ -7316,35 +7306,35 @@
         <f aca="false">1+(O71*2.25)</f>
         <v>8.318125</v>
       </c>
-      <c r="Q71" s="6" t="n">
+      <c r="Q71" s="7" t="n">
         <f aca="false">ROUND(P71,0)</f>
         <v>8</v>
       </c>
-      <c r="R71" s="2" t="s">
+      <c r="R71" s="3" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A72" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="D72" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="E72" s="3" t="s">
         <v>255</v>
       </c>
-    </row>
-    <row r="72" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="B72" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C72" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="D72" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="E72" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="F72" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="G72" s="7" t="s">
-        <v>248</v>
+      <c r="F72" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>60</v>
       </c>
       <c r="H72" s="8" t="n">
         <v>3.2</v>
@@ -7375,35 +7365,35 @@
         <f aca="false">1+(O72*2.25)</f>
         <v>8.36875</v>
       </c>
-      <c r="Q72" s="6" t="n">
+      <c r="Q72" s="7" t="n">
         <f aca="false">ROUND(P72,0)</f>
         <v>8</v>
       </c>
-      <c r="R72" s="2" t="s">
+      <c r="R72" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A73" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="D73" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="E73" s="3" t="s">
         <v>258</v>
       </c>
-    </row>
-    <row r="73" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="B73" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C73" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="D73" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="E73" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="F73" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="G73" s="7" t="s">
-        <v>248</v>
+      <c r="F73" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G73" s="3" t="s">
+        <v>60</v>
       </c>
       <c r="H73" s="8" t="n">
         <v>3.6</v>
@@ -7434,35 +7424,35 @@
         <f aca="false">1+(O73*2.25)</f>
         <v>9.364375</v>
       </c>
-      <c r="Q73" s="6" t="n">
+      <c r="Q73" s="7" t="n">
         <f aca="false">ROUND(P73,0)</f>
         <v>9</v>
       </c>
-      <c r="R73" s="2" t="s">
+      <c r="R73" s="3" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A74" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="D74" s="3" t="s">
         <v>261</v>
       </c>
-    </row>
-    <row r="74" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="B74" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C74" s="2" t="s">
+      <c r="E74" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="D74" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="E74" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="F74" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="G74" s="7" t="s">
-        <v>64</v>
+      <c r="F74" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G74" s="3" t="s">
+        <v>60</v>
       </c>
       <c r="H74" s="8" t="n">
         <v>4</v>
@@ -7493,71 +7483,71 @@
         <f aca="false">1+(O74*2.25)</f>
         <v>9.83125</v>
       </c>
-      <c r="Q74" s="6" t="n">
+      <c r="Q74" s="7" t="n">
         <f aca="false">ROUND(P74,0)</f>
         <v>10</v>
       </c>
-      <c r="R74" s="2" t="s">
+      <c r="R74" s="3" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A75" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="D75" s="1" t="s">
         <v>265</v>
       </c>
-    </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="B75" s="0" t="s">
-        <v>27</v>
-      </c>
-      <c r="C75" s="0" t="s">
+      <c r="E75" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="D75" s="0" t="s">
-        <v>267</v>
-      </c>
-      <c r="E75" s="0" t="s">
-        <v>268</v>
-      </c>
-      <c r="F75" s="0" t="s">
-        <v>64</v>
-      </c>
-      <c r="G75" s="0" t="s">
-        <v>64</v>
-      </c>
-      <c r="H75" s="0" t="n">
+      <c r="F75" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="G75" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="H75" s="1" t="n">
         <v>0.3</v>
       </c>
-      <c r="I75" s="0" t="n">
+      <c r="I75" s="1" t="n">
         <v>0.5</v>
       </c>
-      <c r="J75" s="0" t="n">
+      <c r="J75" s="1" t="n">
         <v>0.2</v>
       </c>
-      <c r="K75" s="0" t="n">
+      <c r="K75" s="1" t="n">
         <v>0.2</v>
       </c>
-      <c r="L75" s="0" t="n">
+      <c r="L75" s="1" t="n">
         <v>0.4</v>
       </c>
-      <c r="M75" s="0" t="n">
+      <c r="M75" s="1" t="n">
         <v>0.2</v>
       </c>
-      <c r="N75" s="0" t="n">
+      <c r="N75" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="O75" s="0" t="n">
+      <c r="O75" s="1" t="n">
         <f aca="false">H75*Methodology!$E$4+I75*Methodology!$E$5+J75*Methodology!$E$6+K75*Methodology!$E$7+L75*Methodology!$E$8+M75*Methodology!$E$9+N75*Methodology!$E$10</f>
         <v>0.37</v>
       </c>
-      <c r="P75" s="0" t="n">
+      <c r="P75" s="1" t="n">
         <f aca="false">1+(O75*2.25)</f>
         <v>1.8325</v>
       </c>
-      <c r="Q75" s="0" t="n">
+      <c r="Q75" s="1" t="n">
         <f aca="false">ROUND(P75,0)</f>
         <v>2</v>
       </c>
-      <c r="R75" s="0" t="s">
-        <v>269</v>
+      <c r="R75" s="1" t="s">
+        <v>267</v>
       </c>
     </row>
   </sheetData>
@@ -7616,14 +7606,14 @@
   <dimension ref="A1:F13"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="22"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B1" s="9"/>
       <c r="C1" s="9"/>
@@ -7631,7 +7621,7 @@
       <c r="E1" s="9"/>
       <c r="F1" s="9"/>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="10" t="s">
         <v>24</v>
       </c>
@@ -7639,20 +7629,20 @@
         <v>25</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="n">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C4" s="0" t="n">
+      <c r="C4" s="1" t="n">
         <f aca="false">COUNTIF(Evaluations!$A$2:$A$200,A4)</f>
         <v>4</v>
       </c>
@@ -7661,14 +7651,14 @@
         <v>1.15890625</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="n">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C5" s="0" t="n">
+      <c r="C5" s="1" t="n">
         <f aca="false">COUNTIF(Evaluations!$A$2:$A$200,A5)</f>
         <v>14</v>
       </c>
@@ -7677,14 +7667,14 @@
         <v>1.85339285714286</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="n">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="0" t="n">
+      <c r="C6" s="1" t="n">
         <f aca="false">COUNTIF(Evaluations!$A$2:$A$200,A6)</f>
         <v>15</v>
       </c>
@@ -7693,14 +7683,14 @@
         <v>2.738125</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="n">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C7" s="0" t="n">
+      <c r="C7" s="1" t="n">
         <f aca="false">COUNTIF(Evaluations!$A$2:$A$200,A7)</f>
         <v>20</v>
       </c>
@@ -7709,14 +7699,14 @@
         <v>3.77340625</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="n">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="B8" s="0" t="s">
+      <c r="B8" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C8" s="0" t="n">
+      <c r="C8" s="1" t="n">
         <f aca="false">COUNTIF(Evaluations!$A$2:$A$200,A8)</f>
         <v>9</v>
       </c>
@@ -7725,14 +7715,14 @@
         <v>4.884375</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="n">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="B9" s="0" t="s">
+      <c r="B9" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C9" s="0" t="n">
+      <c r="C9" s="1" t="n">
         <f aca="false">COUNTIF(Evaluations!$A$2:$A$200,A9)</f>
         <v>5</v>
       </c>
@@ -7741,14 +7731,14 @@
         <v>6.0445</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="n">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="B10" s="0" t="s">
+      <c r="B10" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C10" s="0" t="n">
+      <c r="C10" s="1" t="n">
         <f aca="false">COUNTIF(Evaluations!$A$2:$A$200,A10)</f>
         <v>1</v>
       </c>
@@ -7757,14 +7747,14 @@
         <v>7.31125</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="n">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="B11" s="0" t="s">
+      <c r="B11" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C11" s="0" t="n">
+      <c r="C11" s="1" t="n">
         <f aca="false">COUNTIF(Evaluations!$A$2:$A$200,A11)</f>
         <v>4</v>
       </c>
@@ -7773,14 +7763,14 @@
         <v>8.37859375</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="n">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="B12" s="0" t="s">
+      <c r="B12" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C12" s="0" t="n">
+      <c r="C12" s="1" t="n">
         <f aca="false">COUNTIF(Evaluations!$A$2:$A$200,A12)</f>
         <v>1</v>
       </c>
@@ -7789,14 +7779,14 @@
         <v>9.364375</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="n">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="B13" s="0" t="s">
+      <c r="B13" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C13" s="0" t="n">
+      <c r="C13" s="1" t="n">
         <f aca="false">COUNTIF(Evaluations!$A$2:$A$200,A13)</f>
         <v>1</v>
       </c>

--- a/Fantasy_Grimdark_Scale_Fully_Scored.xlsx
+++ b/Fantasy_Grimdark_Scale_Fully_Scored.xlsx
@@ -168,33 +168,36 @@
     <t xml:space="preserve">Studio Ghibli / Hayao Miyazaki</t>
   </si>
   <si>
+    <t xml:space="preserve">No</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Everyday kindness, family care and healing dominate the worldview.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kiki's Delivery Service</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Low-stakes crisis resolved through community and personal growth.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ponyo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Danger exists, but wonder, love and reconciliation remain central.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Legends &amp; Lattes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Novel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Travis Baldree</t>
+  </si>
+  <si>
     <t xml:space="preserve">Yes</t>
   </si>
   <si>
-    <t xml:space="preserve">Everyday kindness, family care and healing dominate the worldview.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kiki's Delivery Service</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Low-stakes crisis resolved through community and personal growth.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ponyo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Danger exists, but wonder, love and reconciliation remain central.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Legends &amp; Lattes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Novel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Travis Baldree</t>
-  </si>
-  <si>
     <t xml:space="preserve">A flagship cozy fantasy built around community and second chances.</t>
   </si>
   <si>
@@ -202,9 +205,6 @@
   </si>
   <si>
     <t xml:space="preserve">T. J. Klune</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No</t>
   </si>
   <si>
     <t xml:space="preserve">Institutional prejudice is real, but empathy and care can reform lives.</t>
@@ -2184,11 +2184,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="43734253"/>
-        <c:axId val="44364566"/>
+        <c:axId val="11588857"/>
+        <c:axId val="4628358"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="43734253"/>
+        <c:axId val="11588857"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2233,7 +2233,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="44364566"/>
+        <c:crossAx val="4628358"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2241,7 +2241,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="44364566"/>
+        <c:axId val="4628358"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2286,7 +2286,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="43734253"/>
+        <c:crossAx val="11588857"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2543,9 +2543,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>609480</xdr:colOff>
+      <xdr:colOff>609120</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>188640</xdr:rowOff>
+      <xdr:rowOff>188280</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -2554,7 +2554,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="7518960" y="438120"/>
-        <a:ext cx="4890240" cy="3427200"/>
+        <a:ext cx="4889880" cy="3426840"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -3378,7 +3378,7 @@
         <v>56</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>48</v>
@@ -3417,7 +3417,7 @@
         <v>1</v>
       </c>
       <c r="R5" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3428,19 +3428,19 @@
         <v>27</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>55</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="H6" s="8" t="n">
         <v>0.45</v>
@@ -3496,10 +3496,10 @@
         <v>63</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="H7" s="8" t="n">
         <v>0.45</v>
@@ -3555,10 +3555,10 @@
         <v>63</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="H8" s="8" t="n">
         <v>0.45</v>
@@ -3614,7 +3614,7 @@
         <v>69</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>48</v>
@@ -3673,7 +3673,7 @@
         <v>72</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>48</v>
@@ -3732,7 +3732,7 @@
         <v>76</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>48</v>
@@ -3791,7 +3791,7 @@
         <v>76</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>48</v>
@@ -3850,7 +3850,7 @@
         <v>82</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>48</v>
@@ -3909,7 +3909,7 @@
         <v>47</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>48</v>
@@ -3968,7 +3968,7 @@
         <v>47</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>48</v>
@@ -4027,7 +4027,7 @@
         <v>90</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>48</v>
@@ -4086,7 +4086,7 @@
         <v>94</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>48</v>
@@ -4145,7 +4145,7 @@
         <v>97</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>48</v>
@@ -4204,10 +4204,10 @@
         <v>101</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="H19" s="8" t="n">
         <v>0.85</v>
@@ -4263,7 +4263,7 @@
         <v>105</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>48</v>
@@ -4322,7 +4322,7 @@
         <v>109</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>48</v>
@@ -4381,7 +4381,7 @@
         <v>113</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>48</v>
@@ -4440,7 +4440,7 @@
         <v>117</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>48</v>
@@ -4499,7 +4499,7 @@
         <v>47</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>48</v>
@@ -4558,7 +4558,7 @@
         <v>47</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>48</v>
@@ -4617,7 +4617,7 @@
         <v>82</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>48</v>
@@ -4676,7 +4676,7 @@
         <v>90</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>48</v>
@@ -4735,7 +4735,7 @@
         <v>90</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>48</v>
@@ -4794,7 +4794,7 @@
         <v>131</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>48</v>
@@ -4853,7 +4853,7 @@
         <v>76</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>48</v>
@@ -4912,7 +4912,7 @@
         <v>76</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>48</v>
@@ -4971,7 +4971,7 @@
         <v>139</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>48</v>
@@ -5030,7 +5030,7 @@
         <v>142</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>48</v>
@@ -5089,10 +5089,10 @@
         <v>145</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="H34" s="8" t="n">
         <v>1.25</v>
@@ -5148,7 +5148,7 @@
         <v>148</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="G35" s="3" t="s">
         <v>48</v>
@@ -5207,7 +5207,7 @@
         <v>148</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="G36" s="3" t="s">
         <v>48</v>
@@ -5266,10 +5266,10 @@
         <v>82</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="H37" s="8" t="n">
         <v>1.55</v>
@@ -5325,10 +5325,10 @@
         <v>156</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="H38" s="8" t="n">
         <v>1.25</v>
@@ -5384,7 +5384,7 @@
         <v>160</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="G39" s="3" t="s">
         <v>48</v>
@@ -5443,7 +5443,7 @@
         <v>163</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="G40" s="3" t="s">
         <v>48</v>
@@ -5502,10 +5502,10 @@
         <v>76</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="H41" s="8" t="n">
         <v>1.25</v>
@@ -5561,10 +5561,10 @@
         <v>76</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="H42" s="8" t="n">
         <v>1.4</v>
@@ -5620,7 +5620,7 @@
         <v>76</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="G43" s="3" t="s">
         <v>48</v>
@@ -5679,10 +5679,10 @@
         <v>173</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="H44" s="8" t="n">
         <v>1.25</v>
@@ -5738,7 +5738,7 @@
         <v>148</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>48</v>
@@ -5797,10 +5797,10 @@
         <v>179</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="H46" s="8" t="n">
         <v>1.25</v>
@@ -5856,7 +5856,7 @@
         <v>47</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>48</v>
@@ -5915,10 +5915,10 @@
         <v>184</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="H48" s="8" t="n">
         <v>1.25</v>
@@ -5974,7 +5974,7 @@
         <v>187</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="G49" s="3" t="s">
         <v>48</v>
@@ -6033,7 +6033,7 @@
         <v>190</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="G50" s="3" t="s">
         <v>48</v>
@@ -6092,10 +6092,10 @@
         <v>101</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="H51" s="8" t="n">
         <v>1.25</v>
@@ -6151,7 +6151,7 @@
         <v>196</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>48</v>
@@ -6210,10 +6210,10 @@
         <v>47</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="H53" s="8" t="n">
         <v>1.25</v>
@@ -6269,10 +6269,10 @@
         <v>201</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="H54" s="8" t="n">
         <v>1.85</v>
@@ -6328,10 +6328,10 @@
         <v>204</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="H55" s="8" t="n">
         <v>1.85</v>
@@ -6387,10 +6387,10 @@
         <v>90</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="H56" s="8" t="n">
         <v>2</v>
@@ -6446,10 +6446,10 @@
         <v>156</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="H57" s="8" t="n">
         <v>1.7</v>
@@ -6505,10 +6505,10 @@
         <v>90</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="H58" s="8" t="n">
         <v>1.9</v>
@@ -6564,10 +6564,10 @@
         <v>160</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="H59" s="8" t="n">
         <v>1.95</v>
@@ -6623,10 +6623,10 @@
         <v>217</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="H60" s="8" t="n">
         <v>1.95</v>
@@ -6682,10 +6682,10 @@
         <v>220</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="G61" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="H61" s="8" t="n">
         <v>1.9</v>
@@ -6741,10 +6741,10 @@
         <v>223</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="H62" s="8" t="n">
         <v>1.7</v>
@@ -6800,10 +6800,10 @@
         <v>226</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="G63" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="H63" s="8" t="n">
         <v>2.4</v>
@@ -6859,10 +6859,10 @@
         <v>160</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="H64" s="8" t="n">
         <v>2.2</v>
@@ -6918,10 +6918,10 @@
         <v>232</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="G65" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="H65" s="8" t="n">
         <v>2.2</v>
@@ -6977,10 +6977,10 @@
         <v>235</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="H66" s="8" t="n">
         <v>2.35</v>
@@ -7036,10 +7036,10 @@
         <v>239</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="G67" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="H67" s="8" t="n">
         <v>2.2</v>
@@ -7095,10 +7095,10 @@
         <v>243</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="G68" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="H68" s="8" t="n">
         <v>2.95</v>
@@ -7154,10 +7154,10 @@
         <v>246</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="G69" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="H69" s="8" t="n">
         <v>3.2</v>
@@ -7213,10 +7213,10 @@
         <v>249</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="G70" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="H70" s="8" t="n">
         <v>3.5</v>
@@ -7272,10 +7272,10 @@
         <v>252</v>
       </c>
       <c r="F71" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="G71" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="H71" s="8" t="n">
         <v>3.2</v>
@@ -7331,10 +7331,10 @@
         <v>255</v>
       </c>
       <c r="F72" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="G72" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="H72" s="8" t="n">
         <v>3.2</v>
@@ -7390,10 +7390,10 @@
         <v>258</v>
       </c>
       <c r="F73" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="G73" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="H73" s="8" t="n">
         <v>3.6</v>
@@ -7449,10 +7449,10 @@
         <v>262</v>
       </c>
       <c r="F74" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="G74" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="H74" s="8" t="n">
         <v>4</v>
@@ -7508,10 +7508,10 @@
         <v>266</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="H75" s="1" t="n">
         <v>0.3</v>

--- a/Fantasy_Grimdark_Scale_Fully_Scored.xlsx
+++ b/Fantasy_Grimdark_Scale_Fully_Scored.xlsx
@@ -171,6 +171,9 @@
     <t xml:space="preserve">No</t>
   </si>
   <si>
+    <t xml:space="preserve">Yes</t>
+  </si>
+  <si>
     <t xml:space="preserve">Everyday kindness, family care and healing dominate the worldview.</t>
   </si>
   <si>
@@ -193,9 +196,6 @@
   </si>
   <si>
     <t xml:space="preserve">Travis Baldree</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yes</t>
   </si>
   <si>
     <t xml:space="preserve">A flagship cozy fantasy built around community and second chances.</t>
@@ -2184,11 +2184,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="11588857"/>
-        <c:axId val="4628358"/>
+        <c:axId val="38617452"/>
+        <c:axId val="75355639"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="11588857"/>
+        <c:axId val="38617452"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2233,7 +2233,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="4628358"/>
+        <c:crossAx val="75355639"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2241,7 +2241,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="4628358"/>
+        <c:axId val="75355639"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2286,7 +2286,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="11588857"/>
+        <c:crossAx val="38617452"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2543,9 +2543,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>609120</xdr:colOff>
+      <xdr:colOff>608760</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>188280</xdr:rowOff>
+      <xdr:rowOff>187920</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -2554,7 +2554,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="7518960" y="438120"/>
-        <a:ext cx="4889880" cy="3426840"/>
+        <a:ext cx="4889520" cy="3426480"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -3204,7 +3204,7 @@
         <v>48</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H2" s="8" t="n">
         <v>0.1</v>
@@ -3240,7 +3240,7 @@
         <v>1</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3251,7 +3251,7 @@
         <v>26</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>46</v>
@@ -3263,7 +3263,7 @@
         <v>48</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H3" s="8" t="n">
         <v>0.2</v>
@@ -3299,7 +3299,7 @@
         <v>1</v>
       </c>
       <c r="R3" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3310,7 +3310,7 @@
         <v>26</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>46</v>
@@ -3322,7 +3322,7 @@
         <v>48</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H4" s="8" t="n">
         <v>0.1</v>
@@ -3358,7 +3358,7 @@
         <v>1</v>
       </c>
       <c r="R4" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3369,19 +3369,19 @@
         <v>26</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H5" s="8" t="n">
         <v>0.1</v>
@@ -3431,7 +3431,7 @@
         <v>59</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>60</v>
@@ -3440,7 +3440,7 @@
         <v>48</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="H6" s="8" t="n">
         <v>0.45</v>
@@ -3490,7 +3490,7 @@
         <v>62</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>63</v>
@@ -3499,7 +3499,7 @@
         <v>48</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="H7" s="8" t="n">
         <v>0.45</v>
@@ -3549,7 +3549,7 @@
         <v>65</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>63</v>
@@ -3558,7 +3558,7 @@
         <v>48</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="H8" s="8" t="n">
         <v>0.45</v>
@@ -4207,7 +4207,7 @@
         <v>48</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="H19" s="8" t="n">
         <v>0.85</v>
@@ -5083,7 +5083,7 @@
         <v>144</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E34" s="3" t="s">
         <v>145</v>
@@ -5142,7 +5142,7 @@
         <v>147</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E35" s="3" t="s">
         <v>148</v>
@@ -5800,7 +5800,7 @@
         <v>48</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="H46" s="8" t="n">
         <v>1.25</v>

--- a/Fantasy_Grimdark_Scale_Fully_Scored.xlsx
+++ b/Fantasy_Grimdark_Scale_Fully_Scored.xlsx
@@ -2184,11 +2184,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="38617452"/>
-        <c:axId val="75355639"/>
+        <c:axId val="71486027"/>
+        <c:axId val="26757166"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="38617452"/>
+        <c:axId val="71486027"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2233,7 +2233,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="75355639"/>
+        <c:crossAx val="26757166"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2241,7 +2241,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="75355639"/>
+        <c:axId val="26757166"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2286,7 +2286,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="38617452"/>
+        <c:crossAx val="71486027"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2543,9 +2543,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>608760</xdr:colOff>
+      <xdr:colOff>608400</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>187920</xdr:rowOff>
+      <xdr:rowOff>187560</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -2554,7 +2554,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="7518960" y="438120"/>
-        <a:ext cx="4889520" cy="3426480"/>
+        <a:ext cx="4889160" cy="3426120"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -4797,7 +4797,7 @@
         <v>48</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H29" s="8" t="n">
         <v>0.95</v>

--- a/Fantasy_Grimdark_Scale_Fully_Scored.xlsx
+++ b/Fantasy_Grimdark_Scale_Fully_Scored.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="594" uniqueCount="271">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="607" uniqueCount="284">
   <si>
     <t xml:space="preserve">Fantasy Darkness Scale: Methodology</t>
   </si>
@@ -130,6 +130,45 @@
   </si>
   <si>
     <t xml:space="preserve">Very Extreme Grimdark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cozy Fantasy / Hopepunk columns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Descriptive tags only -- excluded from the Weighted Internal Score / Calculated Score formula on purpose. Genre stance toward darkness is not the same as amount of darkness (e.g. Avatar: The Last Airbender is tagged Hopepunk but depicts real war and genocide).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cozy Fantasy = Yes requires</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Genuinely part of that specific book-publishing genre movement (comfort-focused, low-stakes, community/found-family), not just "has a cozy feeling."</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hopepunk = Yes requires one of three variants</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Gentle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No real adversity needed -- kindness/community/anti-cynicism as the default, deliberately-valued state of the world (e.g. Totoro, Legends &amp; Lattes).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Fierce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Real external/societal adversity (an oppressive system, empire, institution) + hope/kindness as active resistance to it (e.g. The House in the Cerulean Sea, Avatar: The Last Airbender).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Bittersweet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Real existential adversity (mortality, loss, the passage of time -- not politically "resistable") + connection/kindness deliberately chosen anyway, knowing it will cost grief later (e.g. Frieren).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not sufficient for any variant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Simply having a hopeful tone or a happy ending. Most tier 1-4 works are correctly Hopepunk = No.</t>
   </si>
   <si>
     <t xml:space="preserve">Work</t>
@@ -2184,11 +2223,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="71486027"/>
-        <c:axId val="26757166"/>
+        <c:axId val="43826828"/>
+        <c:axId val="79257990"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="71486027"/>
+        <c:axId val="43826828"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2233,7 +2272,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="26757166"/>
+        <c:crossAx val="79257990"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2241,7 +2280,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="26757166"/>
+        <c:axId val="79257990"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2286,7 +2325,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="71486027"/>
+        <c:crossAx val="43826828"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2543,9 +2582,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>608400</xdr:colOff>
+      <xdr:colOff>608040</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>187560</xdr:rowOff>
+      <xdr:rowOff>187200</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -2554,7 +2593,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="7518960" y="438120"/>
-        <a:ext cx="4889160" cy="3426120"/>
+        <a:ext cx="4888800" cy="3425760"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -2724,7 +2763,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H32"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="24"/>
@@ -3094,6 +3133,59 @@
       <c r="F24" s="3"/>
       <c r="G24" s="3"/>
       <c r="H24" s="3"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>48</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -3136,19 +3228,19 @@
         <v>25</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="H1" s="6" t="s">
         <v>7</v>
@@ -3172,16 +3264,16 @@
         <v>19</v>
       </c>
       <c r="O1" s="6" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="P1" s="6" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="Q1" s="6" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="R1" s="6" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3192,19 +3284,19 @@
         <v>26</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="H2" s="8" t="n">
         <v>0.1</v>
@@ -3240,7 +3332,7 @@
         <v>1</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3251,19 +3343,19 @@
         <v>26</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="H3" s="8" t="n">
         <v>0.2</v>
@@ -3299,7 +3391,7 @@
         <v>1</v>
       </c>
       <c r="R3" s="3" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3310,19 +3402,19 @@
         <v>26</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="H4" s="8" t="n">
         <v>0.1</v>
@@ -3358,7 +3450,7 @@
         <v>1</v>
       </c>
       <c r="R4" s="3" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3369,19 +3461,19 @@
         <v>26</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="H5" s="8" t="n">
         <v>0.1</v>
@@ -3417,7 +3509,7 @@
         <v>1</v>
       </c>
       <c r="R5" s="3" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3428,19 +3520,19 @@
         <v>27</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="H6" s="8" t="n">
         <v>0.45</v>
@@ -3476,7 +3568,7 @@
         <v>2</v>
       </c>
       <c r="R6" s="3" t="s">
-        <v>61</v>
+        <v>74</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3487,19 +3579,19 @@
         <v>27</v>
       </c>
       <c r="C7" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G7" s="3" t="s">
         <v>62</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>49</v>
       </c>
       <c r="H7" s="8" t="n">
         <v>0.45</v>
@@ -3535,7 +3627,7 @@
         <v>2</v>
       </c>
       <c r="R7" s="3" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3546,19 +3638,19 @@
         <v>27</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="H8" s="8" t="n">
         <v>0.45</v>
@@ -3594,7 +3686,7 @@
         <v>2</v>
       </c>
       <c r="R8" s="3" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3605,19 +3697,19 @@
         <v>27</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="H9" s="8" t="n">
         <v>0.45</v>
@@ -3653,7 +3745,7 @@
         <v>2</v>
       </c>
       <c r="R9" s="3" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3664,19 +3756,19 @@
         <v>27</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="H10" s="8" t="n">
         <v>0.45</v>
@@ -3712,7 +3804,7 @@
         <v>2</v>
       </c>
       <c r="R10" s="3" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3723,19 +3815,19 @@
         <v>27</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="H11" s="8" t="n">
         <v>0.45</v>
@@ -3771,7 +3863,7 @@
         <v>2</v>
       </c>
       <c r="R11" s="3" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3782,19 +3874,19 @@
         <v>27</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="H12" s="8" t="n">
         <v>0.45</v>
@@ -3830,7 +3922,7 @@
         <v>2</v>
       </c>
       <c r="R12" s="3" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3841,19 +3933,19 @@
         <v>27</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="H13" s="8" t="n">
         <v>0.45</v>
@@ -3889,7 +3981,7 @@
         <v>2</v>
       </c>
       <c r="R13" s="3" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3900,19 +3992,19 @@
         <v>27</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="H14" s="8" t="n">
         <v>0.45</v>
@@ -3948,7 +4040,7 @@
         <v>2</v>
       </c>
       <c r="R14" s="3" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3959,19 +4051,19 @@
         <v>27</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="H15" s="8" t="n">
         <v>0.45</v>
@@ -4007,7 +4099,7 @@
         <v>2</v>
       </c>
       <c r="R15" s="3" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4018,19 +4110,19 @@
         <v>27</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="H16" s="8" t="n">
         <v>0.45</v>
@@ -4066,7 +4158,7 @@
         <v>2</v>
       </c>
       <c r="R16" s="3" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4077,19 +4169,19 @@
         <v>27</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>94</v>
+        <v>107</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="H17" s="8" t="n">
         <v>0.45</v>
@@ -4125,7 +4217,7 @@
         <v>2</v>
       </c>
       <c r="R17" s="3" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4136,19 +4228,19 @@
         <v>27</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="H18" s="8" t="n">
         <v>0.45</v>
@@ -4184,7 +4276,7 @@
         <v>2</v>
       </c>
       <c r="R18" s="3" t="s">
-        <v>98</v>
+        <v>111</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4195,19 +4287,19 @@
         <v>28</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="H19" s="8" t="n">
         <v>0.85</v>
@@ -4243,7 +4335,7 @@
         <v>3</v>
       </c>
       <c r="R19" s="3" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4254,19 +4346,19 @@
         <v>28</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>105</v>
+        <v>118</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="H20" s="8" t="n">
         <v>0.85</v>
@@ -4302,7 +4394,7 @@
         <v>3</v>
       </c>
       <c r="R20" s="3" t="s">
-        <v>106</v>
+        <v>119</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4313,19 +4405,19 @@
         <v>28</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>107</v>
+        <v>120</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="H21" s="8" t="n">
         <v>0.85</v>
@@ -4361,7 +4453,7 @@
         <v>3</v>
       </c>
       <c r="R21" s="3" t="s">
-        <v>110</v>
+        <v>123</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4372,19 +4464,19 @@
         <v>28</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>111</v>
+        <v>124</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="H22" s="8" t="n">
         <v>0.85</v>
@@ -4420,7 +4512,7 @@
         <v>3</v>
       </c>
       <c r="R22" s="3" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4431,19 +4523,19 @@
         <v>28</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>117</v>
+        <v>130</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="H23" s="8" t="n">
         <v>0.85</v>
@@ -4479,7 +4571,7 @@
         <v>3</v>
       </c>
       <c r="R23" s="3" t="s">
-        <v>118</v>
+        <v>131</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4490,19 +4582,19 @@
         <v>28</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>119</v>
+        <v>132</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="H24" s="8" t="n">
         <v>0.85</v>
@@ -4538,7 +4630,7 @@
         <v>3</v>
       </c>
       <c r="R24" s="3" t="s">
-        <v>120</v>
+        <v>133</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4549,19 +4641,19 @@
         <v>28</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>121</v>
+        <v>134</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="H25" s="8" t="n">
         <v>1.05</v>
@@ -4597,7 +4689,7 @@
         <v>3</v>
       </c>
       <c r="R25" s="3" t="s">
-        <v>122</v>
+        <v>135</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4608,19 +4700,19 @@
         <v>28</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="H26" s="8" t="n">
         <v>1</v>
@@ -4656,7 +4748,7 @@
         <v>3</v>
       </c>
       <c r="R26" s="3" t="s">
-        <v>124</v>
+        <v>137</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4667,19 +4759,19 @@
         <v>28</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="H27" s="8" t="n">
         <v>0.85</v>
@@ -4715,7 +4807,7 @@
         <v>3</v>
       </c>
       <c r="R27" s="3" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4726,19 +4818,19 @@
         <v>28</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>128</v>
+        <v>141</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="H28" s="8" t="n">
         <v>1</v>
@@ -4774,7 +4866,7 @@
         <v>3</v>
       </c>
       <c r="R28" s="3" t="s">
-        <v>129</v>
+        <v>142</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4785,19 +4877,19 @@
         <v>28</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="H29" s="8" t="n">
         <v>0.95</v>
@@ -4833,7 +4925,7 @@
         <v>3</v>
       </c>
       <c r="R29" s="3" t="s">
-        <v>132</v>
+        <v>145</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4844,19 +4936,19 @@
         <v>28</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>133</v>
+        <v>146</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="H30" s="8" t="n">
         <v>0.85</v>
@@ -4892,7 +4984,7 @@
         <v>3</v>
       </c>
       <c r="R30" s="3" t="s">
-        <v>134</v>
+        <v>147</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4903,19 +4995,19 @@
         <v>28</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>135</v>
+        <v>148</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="H31" s="8" t="n">
         <v>1</v>
@@ -4951,7 +5043,7 @@
         <v>3</v>
       </c>
       <c r="R31" s="3" t="s">
-        <v>136</v>
+        <v>149</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4962,19 +5054,19 @@
         <v>28</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>138</v>
+        <v>151</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="H32" s="8" t="n">
         <v>0.95</v>
@@ -5010,7 +5102,7 @@
         <v>3</v>
       </c>
       <c r="R32" s="3" t="s">
-        <v>140</v>
+        <v>153</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5021,19 +5113,19 @@
         <v>28</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>141</v>
+        <v>154</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>142</v>
+        <v>155</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="H33" s="8" t="n">
         <v>0.85</v>
@@ -5069,7 +5161,7 @@
         <v>3</v>
       </c>
       <c r="R33" s="3" t="s">
-        <v>143</v>
+        <v>156</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5080,19 +5172,19 @@
         <v>29</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>144</v>
+        <v>157</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>145</v>
+        <v>158</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="H34" s="8" t="n">
         <v>1.25</v>
@@ -5128,7 +5220,7 @@
         <v>4</v>
       </c>
       <c r="R34" s="3" t="s">
-        <v>146</v>
+        <v>159</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5139,19 +5231,19 @@
         <v>29</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>147</v>
+        <v>160</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="H35" s="8" t="n">
         <v>1.35</v>
@@ -5187,7 +5279,7 @@
         <v>4</v>
       </c>
       <c r="R35" s="3" t="s">
-        <v>149</v>
+        <v>162</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5198,19 +5290,19 @@
         <v>29</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>150</v>
+        <v>163</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>138</v>
+        <v>151</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="H36" s="8" t="n">
         <v>1.35</v>
@@ -5246,7 +5338,7 @@
         <v>4</v>
       </c>
       <c r="R36" s="3" t="s">
-        <v>151</v>
+        <v>164</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5257,19 +5349,19 @@
         <v>29</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>152</v>
+        <v>165</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>153</v>
+        <v>166</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="H37" s="8" t="n">
         <v>1.55</v>
@@ -5305,7 +5397,7 @@
         <v>4</v>
       </c>
       <c r="R37" s="3" t="s">
-        <v>154</v>
+        <v>167</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5316,19 +5408,19 @@
         <v>29</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="H38" s="8" t="n">
         <v>1.25</v>
@@ -5364,7 +5456,7 @@
         <v>4</v>
       </c>
       <c r="R38" s="3" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5375,19 +5467,19 @@
         <v>29</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>158</v>
+        <v>171</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>159</v>
+        <v>172</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>160</v>
+        <v>173</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="H39" s="8" t="n">
         <v>1.45</v>
@@ -5423,7 +5515,7 @@
         <v>4</v>
       </c>
       <c r="R39" s="3" t="s">
-        <v>161</v>
+        <v>174</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5434,19 +5526,19 @@
         <v>29</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>162</v>
+        <v>175</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>163</v>
+        <v>176</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="H40" s="8" t="n">
         <v>1.25</v>
@@ -5482,7 +5574,7 @@
         <v>4</v>
       </c>
       <c r="R40" s="3" t="s">
-        <v>164</v>
+        <v>177</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5493,19 +5585,19 @@
         <v>29</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="H41" s="8" t="n">
         <v>1.25</v>
@@ -5541,7 +5633,7 @@
         <v>4</v>
       </c>
       <c r="R41" s="3" t="s">
-        <v>166</v>
+        <v>179</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5552,19 +5644,19 @@
         <v>29</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>167</v>
+        <v>180</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="H42" s="8" t="n">
         <v>1.4</v>
@@ -5600,7 +5692,7 @@
         <v>4</v>
       </c>
       <c r="R42" s="3" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5611,19 +5703,19 @@
         <v>29</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>169</v>
+        <v>182</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="H43" s="8" t="n">
         <v>1.25</v>
@@ -5659,7 +5751,7 @@
         <v>4</v>
       </c>
       <c r="R43" s="3" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5670,19 +5762,19 @@
         <v>29</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>171</v>
+        <v>184</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>172</v>
+        <v>185</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>173</v>
+        <v>186</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="H44" s="8" t="n">
         <v>1.25</v>
@@ -5718,7 +5810,7 @@
         <v>4</v>
       </c>
       <c r="R44" s="3" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5729,19 +5821,19 @@
         <v>29</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>175</v>
+        <v>188</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>138</v>
+        <v>151</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="H45" s="8" t="n">
         <v>1.35</v>
@@ -5777,7 +5869,7 @@
         <v>4</v>
       </c>
       <c r="R45" s="3" t="s">
-        <v>176</v>
+        <v>189</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5788,19 +5880,19 @@
         <v>29</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>177</v>
+        <v>190</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>179</v>
+        <v>192</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="H46" s="8" t="n">
         <v>1.25</v>
@@ -5836,7 +5928,7 @@
         <v>4</v>
       </c>
       <c r="R46" s="3" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5847,19 +5939,19 @@
         <v>29</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="H47" s="8" t="n">
         <v>1.4</v>
@@ -5895,7 +5987,7 @@
         <v>4</v>
       </c>
       <c r="R47" s="3" t="s">
-        <v>182</v>
+        <v>195</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5906,19 +5998,19 @@
         <v>29</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="H48" s="8" t="n">
         <v>1.25</v>
@@ -5954,7 +6046,7 @@
         <v>4</v>
       </c>
       <c r="R48" s="3" t="s">
-        <v>185</v>
+        <v>198</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5965,19 +6057,19 @@
         <v>29</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>186</v>
+        <v>199</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="H49" s="8" t="n">
         <v>1.25</v>
@@ -6013,7 +6105,7 @@
         <v>4</v>
       </c>
       <c r="R49" s="3" t="s">
-        <v>188</v>
+        <v>201</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6024,19 +6116,19 @@
         <v>29</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>189</v>
+        <v>202</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>138</v>
+        <v>151</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>190</v>
+        <v>203</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="H50" s="8" t="n">
         <v>1.25</v>
@@ -6072,7 +6164,7 @@
         <v>4</v>
       </c>
       <c r="R50" s="3" t="s">
-        <v>191</v>
+        <v>204</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6083,19 +6175,19 @@
         <v>29</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>192</v>
+        <v>205</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="H51" s="8" t="n">
         <v>1.25</v>
@@ -6131,7 +6223,7 @@
         <v>4</v>
       </c>
       <c r="R51" s="3" t="s">
-        <v>193</v>
+        <v>206</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6142,19 +6234,19 @@
         <v>29</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>195</v>
+        <v>208</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>196</v>
+        <v>209</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="H52" s="8" t="n">
         <v>1.4</v>
@@ -6190,7 +6282,7 @@
         <v>4</v>
       </c>
       <c r="R52" s="3" t="s">
-        <v>197</v>
+        <v>210</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6201,19 +6293,19 @@
         <v>29</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>198</v>
+        <v>211</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="H53" s="8" t="n">
         <v>1.25</v>
@@ -6249,7 +6341,7 @@
         <v>4</v>
       </c>
       <c r="R53" s="3" t="s">
-        <v>199</v>
+        <v>212</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6260,19 +6352,19 @@
         <v>30</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>200</v>
+        <v>213</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>138</v>
+        <v>151</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>201</v>
+        <v>214</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="H54" s="8" t="n">
         <v>1.85</v>
@@ -6308,7 +6400,7 @@
         <v>5</v>
       </c>
       <c r="R54" s="3" t="s">
-        <v>202</v>
+        <v>215</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6319,19 +6411,19 @@
         <v>30</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>203</v>
+        <v>216</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="H55" s="8" t="n">
         <v>1.85</v>
@@ -6367,7 +6459,7 @@
         <v>5</v>
       </c>
       <c r="R55" s="3" t="s">
-        <v>205</v>
+        <v>218</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6378,19 +6470,19 @@
         <v>30</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>206</v>
+        <v>219</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="H56" s="8" t="n">
         <v>2</v>
@@ -6426,7 +6518,7 @@
         <v>5</v>
       </c>
       <c r="R56" s="3" t="s">
-        <v>207</v>
+        <v>220</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6437,19 +6529,19 @@
         <v>30</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>208</v>
+        <v>221</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>209</v>
+        <v>222</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="H57" s="8" t="n">
         <v>1.7</v>
@@ -6485,7 +6577,7 @@
         <v>5</v>
       </c>
       <c r="R57" s="3" t="s">
-        <v>210</v>
+        <v>223</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6496,19 +6588,19 @@
         <v>30</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>211</v>
+        <v>224</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="H58" s="8" t="n">
         <v>1.9</v>
@@ -6544,7 +6636,7 @@
         <v>5</v>
       </c>
       <c r="R58" s="3" t="s">
-        <v>212</v>
+        <v>225</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6555,19 +6647,19 @@
         <v>30</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>213</v>
+        <v>226</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>160</v>
+        <v>173</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="H59" s="8" t="n">
         <v>1.95</v>
@@ -6603,7 +6695,7 @@
         <v>5</v>
       </c>
       <c r="R59" s="3" t="s">
-        <v>214</v>
+        <v>227</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6614,19 +6706,19 @@
         <v>30</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>215</v>
+        <v>228</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>216</v>
+        <v>229</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>217</v>
+        <v>230</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="H60" s="8" t="n">
         <v>1.95</v>
@@ -6662,7 +6754,7 @@
         <v>5</v>
       </c>
       <c r="R60" s="3" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6673,19 +6765,19 @@
         <v>30</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>219</v>
+        <v>232</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>220</v>
+        <v>233</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="G61" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="H61" s="8" t="n">
         <v>1.9</v>
@@ -6721,7 +6813,7 @@
         <v>5</v>
       </c>
       <c r="R61" s="3" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6732,19 +6824,19 @@
         <v>30</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>222</v>
+        <v>235</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>223</v>
+        <v>236</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="H62" s="8" t="n">
         <v>1.7</v>
@@ -6780,7 +6872,7 @@
         <v>5</v>
       </c>
       <c r="R62" s="3" t="s">
-        <v>224</v>
+        <v>237</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6791,19 +6883,19 @@
         <v>31</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>225</v>
+        <v>238</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>226</v>
+        <v>239</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="G63" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="H63" s="8" t="n">
         <v>2.4</v>
@@ -6839,7 +6931,7 @@
         <v>6</v>
       </c>
       <c r="R63" s="3" t="s">
-        <v>227</v>
+        <v>240</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6850,19 +6942,19 @@
         <v>31</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>228</v>
+        <v>241</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>160</v>
+        <v>173</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="H64" s="8" t="n">
         <v>2.2</v>
@@ -6898,7 +6990,7 @@
         <v>6</v>
       </c>
       <c r="R64" s="3" t="s">
-        <v>229</v>
+        <v>242</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6909,19 +7001,19 @@
         <v>31</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>230</v>
+        <v>243</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>231</v>
+        <v>244</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>232</v>
+        <v>245</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="G65" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="H65" s="8" t="n">
         <v>2.2</v>
@@ -6957,7 +7049,7 @@
         <v>6</v>
       </c>
       <c r="R65" s="3" t="s">
-        <v>233</v>
+        <v>246</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6968,19 +7060,19 @@
         <v>31</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>234</v>
+        <v>247</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>235</v>
+        <v>248</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="H66" s="8" t="n">
         <v>2.35</v>
@@ -7016,7 +7108,7 @@
         <v>6</v>
       </c>
       <c r="R66" s="3" t="s">
-        <v>236</v>
+        <v>249</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7027,19 +7119,19 @@
         <v>31</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>237</v>
+        <v>250</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>238</v>
+        <v>251</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>239</v>
+        <v>252</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="G67" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="H67" s="8" t="n">
         <v>2.2</v>
@@ -7075,7 +7167,7 @@
         <v>6</v>
       </c>
       <c r="R67" s="3" t="s">
-        <v>240</v>
+        <v>253</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7086,19 +7178,19 @@
         <v>32</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>241</v>
+        <v>254</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>242</v>
+        <v>255</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>243</v>
+        <v>256</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="G68" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="H68" s="8" t="n">
         <v>2.95</v>
@@ -7134,7 +7226,7 @@
         <v>7</v>
       </c>
       <c r="R68" s="3" t="s">
-        <v>244</v>
+        <v>257</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7145,19 +7237,19 @@
         <v>33</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>195</v>
+        <v>208</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>246</v>
+        <v>259</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="G69" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="H69" s="8" t="n">
         <v>3.2</v>
@@ -7193,7 +7285,7 @@
         <v>8</v>
       </c>
       <c r="R69" s="3" t="s">
-        <v>247</v>
+        <v>260</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7204,19 +7296,19 @@
         <v>33</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>248</v>
+        <v>261</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>249</v>
+        <v>262</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="G70" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="H70" s="8" t="n">
         <v>3.5</v>
@@ -7252,7 +7344,7 @@
         <v>8</v>
       </c>
       <c r="R70" s="3" t="s">
-        <v>250</v>
+        <v>263</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7263,19 +7355,19 @@
         <v>33</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>251</v>
+        <v>264</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>252</v>
+        <v>265</v>
       </c>
       <c r="F71" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="G71" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="H71" s="8" t="n">
         <v>3.2</v>
@@ -7311,7 +7403,7 @@
         <v>8</v>
       </c>
       <c r="R71" s="3" t="s">
-        <v>253</v>
+        <v>266</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7322,19 +7414,19 @@
         <v>33</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>254</v>
+        <v>267</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>172</v>
+        <v>185</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>255</v>
+        <v>268</v>
       </c>
       <c r="F72" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="G72" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="H72" s="8" t="n">
         <v>3.2</v>
@@ -7370,7 +7462,7 @@
         <v>8</v>
       </c>
       <c r="R72" s="3" t="s">
-        <v>256</v>
+        <v>269</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7381,19 +7473,19 @@
         <v>34</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>257</v>
+        <v>270</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>138</v>
+        <v>151</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>258</v>
+        <v>271</v>
       </c>
       <c r="F73" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="G73" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="H73" s="8" t="n">
         <v>3.6</v>
@@ -7429,7 +7521,7 @@
         <v>9</v>
       </c>
       <c r="R73" s="3" t="s">
-        <v>259</v>
+        <v>272</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7440,19 +7532,19 @@
         <v>35</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>260</v>
+        <v>273</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>261</v>
+        <v>274</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>262</v>
+        <v>275</v>
       </c>
       <c r="F74" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="G74" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="H74" s="8" t="n">
         <v>4</v>
@@ -7488,7 +7580,7 @@
         <v>10</v>
       </c>
       <c r="R74" s="3" t="s">
-        <v>263</v>
+        <v>276</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7499,19 +7591,19 @@
         <v>27</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>264</v>
+        <v>277</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>265</v>
+        <v>278</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>266</v>
+        <v>279</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="H75" s="1" t="n">
         <v>0.3</v>
@@ -7547,7 +7639,7 @@
         <v>2</v>
       </c>
       <c r="R75" s="1" t="s">
-        <v>267</v>
+        <v>280</v>
       </c>
     </row>
   </sheetData>
@@ -7613,7 +7705,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>268</v>
+        <v>281</v>
       </c>
       <c r="B1" s="9"/>
       <c r="C1" s="9"/>
@@ -7629,10 +7721,10 @@
         <v>25</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>269</v>
+        <v>282</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>270</v>
+        <v>283</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">

--- a/Fantasy_Grimdark_Scale_Fully_Scored.xlsx
+++ b/Fantasy_Grimdark_Scale_Fully_Scored.xlsx
@@ -102,16 +102,16 @@
     <t xml:space="preserve">Category</t>
   </si>
   <si>
-    <t xml:space="preserve">Cozy Fantasy, Hopepunk &amp; Very Bright Fantasy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hopepunk, Cozy Fantasy &amp; Heroic Fantasy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Balanced, Melancholic or Hopepunk Fantasy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dark Fantasy with Hope</t>
+    <t xml:space="preserve">Wholesome Cozy Fantasy, Gentle Hopepunk &amp; Very Bright Fantasy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resilient Cozy Fantasy, Fierce Hopepunk &amp; Heroic Fantasy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Balanced, Bittersweet Hopepunk or Melancholic Fantasy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fantasy in Gray Tones</t>
   </si>
   <si>
     <t xml:space="preserve">Gloomy Fantasy</t>
@@ -2223,11 +2223,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="43826828"/>
-        <c:axId val="79257990"/>
+        <c:axId val="26245704"/>
+        <c:axId val="52466607"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="43826828"/>
+        <c:axId val="26245704"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2272,7 +2272,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="79257990"/>
+        <c:crossAx val="52466607"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2280,7 +2280,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="79257990"/>
+        <c:axId val="52466607"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2325,7 +2325,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="43826828"/>
+        <c:crossAx val="26245704"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2582,9 +2582,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>608040</xdr:colOff>
+      <xdr:colOff>607680</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>187200</xdr:rowOff>
+      <xdr:rowOff>186840</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -2593,7 +2593,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="7518960" y="438120"/>
-        <a:ext cx="4888800" cy="3425760"/>
+        <a:ext cx="4888440" cy="3425400"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -3134,7 +3134,7 @@
       <c r="G24" s="3"/>
       <c r="H24" s="3"/>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
         <v>36</v>
       </c>
@@ -3142,7 +3142,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
         <v>38</v>
       </c>
@@ -3150,12 +3150,12 @@
         <v>39</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
         <v>41</v>
       </c>
@@ -3163,7 +3163,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
         <v>43</v>
       </c>
@@ -3171,7 +3171,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
         <v>45</v>
       </c>
@@ -3179,7 +3179,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
         <v>47</v>
       </c>

--- a/Fantasy_Grimdark_Scale_Fully_Scored.xlsx
+++ b/Fantasy_Grimdark_Scale_Fully_Scored.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
-  <fileVersion appName="Calc" lowestEdited="4"/>
+  <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="607" uniqueCount="284">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="614" uniqueCount="288">
   <si>
     <t xml:space="preserve">Fantasy Darkness Scale: Methodology</t>
   </si>
@@ -865,6 +865,18 @@
   </si>
   <si>
     <t xml:space="preserve">A gentle, melancholic fable about loss, love, and learning to truly see — treated with poignant restraint rather than grimness.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adventure Time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TV / Comics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pendleton Ward</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The post-Mushroom-War setting and Ice King's tragic loss of self add real melancholy, but whimsical humor and consistently effective heroism keep the tone gentle overall.</t>
   </si>
   <si>
     <t xml:space="preserve">Fantasy Darkness Scale Summary</t>
@@ -2194,7 +2206,7 @@
                   <c:v>14</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>15</c:v>
+                  <c:v>16</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>20</c:v>
@@ -2223,11 +2235,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="26245704"/>
-        <c:axId val="52466607"/>
+        <c:axId val="10681028"/>
+        <c:axId val="15025122"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="26245704"/>
+        <c:axId val="10681028"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2272,7 +2284,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="52466607"/>
+        <c:crossAx val="15025122"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2280,7 +2292,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="52466607"/>
+        <c:axId val="15025122"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2325,7 +2337,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="26245704"/>
+        <c:crossAx val="10681028"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2582,9 +2594,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>607680</xdr:colOff>
+      <xdr:colOff>607320</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>186840</xdr:rowOff>
+      <xdr:rowOff>186480</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -2593,7 +2605,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="7518960" y="438120"/>
-        <a:ext cx="4888440" cy="3425400"/>
+        <a:ext cx="4888080" cy="3425040"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -3206,7 +3218,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:R75"/>
+  <dimension ref="A1:R76"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8"/>
@@ -7640,6 +7652,65 @@
       </c>
       <c r="R75" s="1" t="s">
         <v>280</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="E76" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="F76" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="G76" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="H76" s="1" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="I76" s="1" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J76" s="1" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K76" s="1" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="L76" s="1" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="M76" s="1" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N76" s="1" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="O76" s="1" t="n">
+        <f aca="false">H76*Methodology!$E$4+I76*Methodology!$E$5+J76*Methodology!$E$6+K76*Methodology!$E$7+L76*Methodology!$E$8+M76*Methodology!$E$9+N76*Methodology!$E$10</f>
+        <v>0.745</v>
+      </c>
+      <c r="P76" s="1" t="n">
+        <f aca="false">1+(O76*2.25)</f>
+        <v>2.67625</v>
+      </c>
+      <c r="Q76" s="1" t="n">
+        <f aca="false">ROUND(P76,0)</f>
+        <v>3</v>
+      </c>
+      <c r="R76" s="1" t="s">
+        <v>284</v>
       </c>
     </row>
   </sheetData>
@@ -7705,7 +7776,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="B1" s="9"/>
       <c r="C1" s="9"/>
@@ -7721,10 +7792,10 @@
         <v>25</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7768,11 +7839,11 @@
       </c>
       <c r="C6" s="1" t="n">
         <f aca="false">COUNTIF(Evaluations!$A$2:$A$200,A6)</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D6" s="11" t="n">
         <f aca="false">AVERAGEIF(Evaluations!$A$2:$A$200,A6,Evaluations!$P$2:$P$200)</f>
-        <v>2.738125</v>
+        <v>2.7342578125</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">

--- a/Fantasy_Grimdark_Scale_Fully_Scored.xlsx
+++ b/Fantasy_Grimdark_Scale_Fully_Scored.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="614" uniqueCount="288">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="621" uniqueCount="291">
   <si>
     <t xml:space="preserve">Fantasy Darkness Scale: Methodology</t>
   </si>
@@ -877,6 +877,15 @@
   </si>
   <si>
     <t xml:space="preserve">The post-Mushroom-War setting and Ice King's tragic loss of self add real melancholy, but whimsical humor and consistently effective heroism keep the tone gentle overall.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Star vs. the Forces of Evil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daron Nefcy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generations of Mewman genocide against Monsters drive the later seasons, and the finale resolves the conflict by erasing magic outright rather than reforming the system — heavier than most gray-tones peers, though Star's reconciliation arc and the show's comedic early seasons keep real hope in the frame.</t>
   </si>
   <si>
     <t xml:space="preserve">Fantasy Darkness Scale Summary</t>
@@ -2209,7 +2218,7 @@
                   <c:v>16</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>20</c:v>
+                  <c:v>21</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>9</c:v>
@@ -2235,11 +2244,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="10681028"/>
-        <c:axId val="15025122"/>
+        <c:axId val="73284355"/>
+        <c:axId val="81184856"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="10681028"/>
+        <c:axId val="73284355"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2284,7 +2293,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="15025122"/>
+        <c:crossAx val="81184856"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2292,7 +2301,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="15025122"/>
+        <c:axId val="81184856"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2337,7 +2346,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="10681028"/>
+        <c:crossAx val="73284355"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2594,9 +2603,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>607320</xdr:colOff>
+      <xdr:colOff>606960</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>186480</xdr:rowOff>
+      <xdr:rowOff>186120</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -2605,7 +2614,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="7518960" y="438120"/>
-        <a:ext cx="4888080" cy="3425040"/>
+        <a:ext cx="4887720" cy="3424680"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -3218,7 +3227,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:R76"/>
+  <dimension ref="A1:R77"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8"/>
@@ -7654,7 +7663,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="1" t="n">
         <v>3</v>
       </c>
@@ -7711,6 +7720,65 @@
       </c>
       <c r="R76" s="1" t="s">
         <v>284</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="E77" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="F77" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="G77" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="H77" s="1" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I77" s="1" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="J77" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K77" s="1" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L77" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M77" s="1" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="N77" s="1" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="O77" s="1" t="n">
+        <f aca="false">H77*Methodology!$E$4+I77*Methodology!$E$5+J77*Methodology!$E$6+K77*Methodology!$E$7+L77*Methodology!$E$8+M77*Methodology!$E$9+N77*Methodology!$E$10</f>
+        <v>1.2225</v>
+      </c>
+      <c r="P77" s="1" t="n">
+        <f aca="false">1+(O77*2.25)</f>
+        <v>3.750625</v>
+      </c>
+      <c r="Q77" s="1" t="n">
+        <f aca="false">ROUND(P77,0)</f>
+        <v>4</v>
+      </c>
+      <c r="R77" s="1" t="s">
+        <v>287</v>
       </c>
     </row>
   </sheetData>
@@ -7776,7 +7844,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="B1" s="9"/>
       <c r="C1" s="9"/>
@@ -7792,10 +7860,10 @@
         <v>25</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7855,11 +7923,11 @@
       </c>
       <c r="C7" s="1" t="n">
         <f aca="false">COUNTIF(Evaluations!$A$2:$A$200,A7)</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D7" s="11" t="n">
         <f aca="false">AVERAGEIF(Evaluations!$A$2:$A$200,A7,Evaluations!$P$2:$P$200)</f>
-        <v>3.77340625</v>
+        <v>3.77232142857143</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">

--- a/Fantasy_Grimdark_Scale_Fully_Scored.xlsx
+++ b/Fantasy_Grimdark_Scale_Fully_Scored.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="621" uniqueCount="291">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="628" uniqueCount="294">
   <si>
     <t xml:space="preserve">Fantasy Darkness Scale: Methodology</t>
   </si>
@@ -886,6 +886,15 @@
   </si>
   <si>
     <t xml:space="preserve">Generations of Mewman genocide against Monsters drive the later seasons, and the finale resolves the conflict by erasing magic outright rather than reforming the system — heavier than most gray-tones peers, though Star's reconciliation arc and the show's comedic early seasons keep real hope in the frame.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clevatess</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yūji Iwahara</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A demon king raising a human infant instead of annihilating humanity is genuinely tender, but the surrounding world is severe — infant trafficking and experimentation, and a named character's backstory of sustained abuse push explicit darkness above most of this tier.</t>
   </si>
   <si>
     <t xml:space="preserve">Fantasy Darkness Scale Summary</t>
@@ -2224,7 +2233,7 @@
                   <c:v>9</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>5</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>1</c:v>
@@ -2244,11 +2253,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="73284355"/>
-        <c:axId val="81184856"/>
+        <c:axId val="79935928"/>
+        <c:axId val="93522527"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="73284355"/>
+        <c:axId val="79935928"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2293,7 +2302,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="81184856"/>
+        <c:crossAx val="93522527"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2301,7 +2310,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="81184856"/>
+        <c:axId val="93522527"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2346,7 +2355,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="73284355"/>
+        <c:crossAx val="79935928"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2603,9 +2612,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>606960</xdr:colOff>
+      <xdr:colOff>606600</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>186120</xdr:rowOff>
+      <xdr:rowOff>185760</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -2614,7 +2623,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="7518960" y="438120"/>
-        <a:ext cx="4887720" cy="3424680"/>
+        <a:ext cx="4887360" cy="3424320"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -3227,7 +3236,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:R77"/>
+  <dimension ref="A1:R78"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8"/>
@@ -7722,7 +7731,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="1" t="n">
         <v>4</v>
       </c>
@@ -7779,6 +7788,65 @@
       </c>
       <c r="R77" s="1" t="s">
         <v>287</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E78" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="F78" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="G78" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="H78" s="1" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="I78" s="1" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J78" s="1" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="K78" s="1" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="L78" s="1" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="M78" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="N78" s="1" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O78" s="1" t="n">
+        <f aca="false">H78*Methodology!$E$4+I78*Methodology!$E$5+J78*Methodology!$E$6+K78*Methodology!$E$7+L78*Methodology!$E$8+M78*Methodology!$E$9+N78*Methodology!$E$10</f>
+        <v>2.155</v>
+      </c>
+      <c r="P78" s="1" t="n">
+        <f aca="false">1+(O78*2.25)</f>
+        <v>5.84875</v>
+      </c>
+      <c r="Q78" s="1" t="n">
+        <f aca="false">ROUND(P78,0)</f>
+        <v>6</v>
+      </c>
+      <c r="R78" s="1" t="s">
+        <v>290</v>
       </c>
     </row>
   </sheetData>
@@ -7844,7 +7912,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="B1" s="9"/>
       <c r="C1" s="9"/>
@@ -7860,10 +7928,10 @@
         <v>25</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7955,11 +8023,11 @@
       </c>
       <c r="C9" s="1" t="n">
         <f aca="false">COUNTIF(Evaluations!$A$2:$A$200,A9)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D9" s="11" t="n">
         <f aca="false">AVERAGEIF(Evaluations!$A$2:$A$200,A9,Evaluations!$P$2:$P$200)</f>
-        <v>6.0445</v>
+        <v>6.011875</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">

--- a/Fantasy_Grimdark_Scale_Fully_Scored.xlsx
+++ b/Fantasy_Grimdark_Scale_Fully_Scored.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="628" uniqueCount="294">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="635" uniqueCount="298">
   <si>
     <t xml:space="preserve">Fantasy Darkness Scale: Methodology</t>
   </si>
@@ -895,6 +895,18 @@
   </si>
   <si>
     <t xml:space="preserve">A demon king raising a human infant instead of annihilating humanity is genuinely tender, but the surrounding world is severe — infant trafficking and experimentation, and a named character's backstory of sustained abuse push explicit darkness above most of this tier.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Saga of Tanya the Evil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Light Novels / Manga / Anime / Film</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carlo Zen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A reincarnated corporate pragmatist becomes a ruthlessly effective officer in a magic-augmented World War I that never ends; the satire's thesis is that cynicism outperforms idealism, and neither Tanya nor the war itself ever really changes.</t>
   </si>
   <si>
     <t xml:space="preserve">Fantasy Darkness Scale Summary</t>
@@ -2236,7 +2248,7 @@
                   <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>4</c:v>
@@ -2253,11 +2265,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="79935928"/>
-        <c:axId val="93522527"/>
+        <c:axId val="80746475"/>
+        <c:axId val="19812678"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="79935928"/>
+        <c:axId val="80746475"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2302,7 +2314,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="93522527"/>
+        <c:crossAx val="19812678"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2310,7 +2322,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="93522527"/>
+        <c:axId val="19812678"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2355,7 +2367,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="79935928"/>
+        <c:crossAx val="80746475"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2612,9 +2624,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>606600</xdr:colOff>
+      <xdr:colOff>606240</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>185760</xdr:rowOff>
+      <xdr:rowOff>185400</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -2623,7 +2635,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="7518960" y="438120"/>
-        <a:ext cx="4887360" cy="3424320"/>
+        <a:ext cx="4887000" cy="3423960"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -3236,7 +3248,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:R78"/>
+  <dimension ref="A1:R79"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8"/>
@@ -7790,7 +7802,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="1" t="n">
         <v>6</v>
       </c>
@@ -7847,6 +7859,65 @@
       </c>
       <c r="R78" s="1" t="s">
         <v>290</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="E79" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="F79" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="G79" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="H79" s="1" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I79" s="1" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="J79" s="1" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K79" s="1" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="L79" s="1" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="M79" s="1" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="N79" s="1" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O79" s="1" t="n">
+        <f aca="false">H79*Methodology!$E$4+I79*Methodology!$E$5+J79*Methodology!$E$6+K79*Methodology!$E$7+L79*Methodology!$E$8+M79*Methodology!$E$9+N79*Methodology!$E$10</f>
+        <v>2.8</v>
+      </c>
+      <c r="P79" s="1" t="n">
+        <f aca="false">1+(O79*2.25)</f>
+        <v>7.3</v>
+      </c>
+      <c r="Q79" s="1" t="n">
+        <f aca="false">ROUND(P79,0)</f>
+        <v>7</v>
+      </c>
+      <c r="R79" s="1" t="s">
+        <v>294</v>
       </c>
     </row>
   </sheetData>
@@ -7912,7 +7983,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="B1" s="9"/>
       <c r="C1" s="9"/>
@@ -7928,10 +7999,10 @@
         <v>25</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8039,11 +8110,11 @@
       </c>
       <c r="C10" s="1" t="n">
         <f aca="false">COUNTIF(Evaluations!$A$2:$A$200,A10)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D10" s="11" t="n">
         <f aca="false">AVERAGEIF(Evaluations!$A$2:$A$200,A10,Evaluations!$P$2:$P$200)</f>
-        <v>7.31125</v>
+        <v>7.305625</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">

--- a/Fantasy_Grimdark_Scale_Fully_Scored.xlsx
+++ b/Fantasy_Grimdark_Scale_Fully_Scored.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="635" uniqueCount="298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="642" uniqueCount="301">
   <si>
     <t xml:space="preserve">Fantasy Darkness Scale: Methodology</t>
   </si>
@@ -907,6 +907,15 @@
   </si>
   <si>
     <t xml:space="preserve">A reincarnated corporate pragmatist becomes a ruthlessly effective officer in a magic-augmented World War I that never ends; the satire's thesis is that cynicism outperforms idealism, and neither Tanya nor the war itself ever really changes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Re:Zero − Starting Life in Another World</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tappei Nagatsuki</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Subaru's “Return by Death” turns failure into genuinely repeated, graphic trauma — among the most psychologically brutal content on this scale — but the loops consistently let heroism and hard-won found-family actually fix things, so it stays a story about earning growth through suffering rather than accepting defeat.</t>
   </si>
   <si>
     <t xml:space="preserve">Fantasy Darkness Scale Summary</t>
@@ -2245,7 +2254,7 @@
                   <c:v>9</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>6</c:v>
+                  <c:v>7</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>2</c:v>
@@ -2265,11 +2274,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="80746475"/>
-        <c:axId val="19812678"/>
+        <c:axId val="9167800"/>
+        <c:axId val="31666420"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="80746475"/>
+        <c:axId val="9167800"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2314,7 +2323,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="19812678"/>
+        <c:crossAx val="31666420"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2322,7 +2331,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="19812678"/>
+        <c:axId val="31666420"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2367,7 +2376,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="80746475"/>
+        <c:crossAx val="9167800"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2624,9 +2633,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>606240</xdr:colOff>
+      <xdr:colOff>605880</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>185400</xdr:rowOff>
+      <xdr:rowOff>185040</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -2635,7 +2644,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="7518960" y="438120"/>
-        <a:ext cx="4887000" cy="3423960"/>
+        <a:ext cx="4886640" cy="3423600"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -3248,7 +3257,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:R79"/>
+  <dimension ref="A1:R80"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8"/>
@@ -7861,7 +7870,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="1" t="n">
         <v>7</v>
       </c>
@@ -7918,6 +7927,65 @@
       </c>
       <c r="R79" s="1" t="s">
         <v>294</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="E80" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="F80" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="G80" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="H80" s="1" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="I80" s="1" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J80" s="1" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="K80" s="1" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="L80" s="1" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="M80" s="1" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="N80" s="1" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O80" s="1" t="n">
+        <f aca="false">H80*Methodology!$E$4+I80*Methodology!$E$5+J80*Methodology!$E$6+K80*Methodology!$E$7+L80*Methodology!$E$8+M80*Methodology!$E$9+N80*Methodology!$E$10</f>
+        <v>2.14</v>
+      </c>
+      <c r="P80" s="1" t="n">
+        <f aca="false">1+(O80*2.25)</f>
+        <v>5.815</v>
+      </c>
+      <c r="Q80" s="1" t="n">
+        <f aca="false">ROUND(P80,0)</f>
+        <v>6</v>
+      </c>
+      <c r="R80" s="1" t="s">
+        <v>297</v>
       </c>
     </row>
   </sheetData>
@@ -7983,7 +8051,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="B1" s="9"/>
       <c r="C1" s="9"/>
@@ -7999,10 +8067,10 @@
         <v>25</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8094,11 +8162,11 @@
       </c>
       <c r="C9" s="1" t="n">
         <f aca="false">COUNTIF(Evaluations!$A$2:$A$200,A9)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D9" s="11" t="n">
         <f aca="false">AVERAGEIF(Evaluations!$A$2:$A$200,A9,Evaluations!$P$2:$P$200)</f>
-        <v>6.011875</v>
+        <v>5.98375</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">

--- a/Fantasy_Grimdark_Scale_Fully_Scored.xlsx
+++ b/Fantasy_Grimdark_Scale_Fully_Scored.xlsx
@@ -120,10 +120,10 @@
     <t xml:space="preserve">Dark Fantasy</t>
   </si>
   <si>
+    <t xml:space="preserve">Extreme Dark Fantasy</t>
+  </si>
+  <si>
     <t xml:space="preserve">Grimdark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Intense Grimdark</t>
   </si>
   <si>
     <t xml:space="preserve">Extreme Grimdark</t>
@@ -2274,11 +2274,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="9167800"/>
-        <c:axId val="31666420"/>
+        <c:axId val="49869824"/>
+        <c:axId val="88565798"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="9167800"/>
+        <c:axId val="49869824"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2323,7 +2323,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="31666420"/>
+        <c:crossAx val="88565798"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2331,7 +2331,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="31666420"/>
+        <c:axId val="88565798"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2376,7 +2376,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="9167800"/>
+        <c:crossAx val="49869824"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2633,9 +2633,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>605880</xdr:colOff>
+      <xdr:colOff>605520</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>185040</xdr:rowOff>
+      <xdr:rowOff>184680</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -2644,7 +2644,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="7518960" y="438120"/>
-        <a:ext cx="4886640" cy="3423600"/>
+        <a:ext cx="4886280" cy="3423240"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -7929,7 +7929,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="1" t="n">
         <v>6</v>
       </c>

--- a/Fantasy_Grimdark_Scale_Fully_Scored.xlsx
+++ b/Fantasy_Grimdark_Scale_Fully_Scored.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="642" uniqueCount="301">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="649" uniqueCount="304">
   <si>
     <t xml:space="preserve">Fantasy Darkness Scale: Methodology</t>
   </si>
@@ -916,6 +916,15 @@
   </si>
   <si>
     <t xml:space="preserve">Subaru's “Return by Death” turns failure into genuinely repeated, graphic trauma — among the most psychologically brutal content on this scale — but the loops consistently let heroism and hard-won found-family actually fix things, so it stays a story about earning growth through suffering rather than accepting defeat.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Legend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ridley Scott</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A mythic, single-villain fairy tale rather than anything institutional: Darkness's gothic menace and the stallion unicorn's death carry real atmospheric horror, but heroism is straightforward and decisive, and Lili's temptation is treated as innocence exploited rather than culpability.</t>
   </si>
   <si>
     <t xml:space="preserve">Fantasy Darkness Scale Summary</t>
@@ -2242,7 +2251,7 @@
                   <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>14</c:v>
+                  <c:v>15</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>16</c:v>
@@ -2274,11 +2283,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="49869824"/>
-        <c:axId val="88565798"/>
+        <c:axId val="17943322"/>
+        <c:axId val="22242778"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="49869824"/>
+        <c:axId val="17943322"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2323,7 +2332,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="88565798"/>
+        <c:crossAx val="22242778"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2331,7 +2340,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="88565798"/>
+        <c:axId val="22242778"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2376,7 +2385,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="49869824"/>
+        <c:crossAx val="17943322"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2633,9 +2642,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>605520</xdr:colOff>
+      <xdr:colOff>605160</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>184680</xdr:rowOff>
+      <xdr:rowOff>184320</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -2644,7 +2653,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="7518960" y="438120"/>
-        <a:ext cx="4886280" cy="3423240"/>
+        <a:ext cx="4885920" cy="3422880"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -3257,7 +3266,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:R80"/>
+  <dimension ref="A1:R81"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8"/>
@@ -7986,6 +7995,65 @@
       </c>
       <c r="R80" s="1" t="s">
         <v>297</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="D81" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E81" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="F81" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="G81" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="H81" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I81" s="1" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="J81" s="1" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="K81" s="1" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="L81" s="1" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M81" s="1" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="N81" s="1" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="O81" s="1" t="n">
+        <f aca="false">H81*Methodology!$E$4+I81*Methodology!$E$5+J81*Methodology!$E$6+K81*Methodology!$E$7+L81*Methodology!$E$8+M81*Methodology!$E$9+N81*Methodology!$E$10</f>
+        <v>0.405</v>
+      </c>
+      <c r="P81" s="1" t="n">
+        <f aca="false">1+(O81*2.25)</f>
+        <v>1.91125</v>
+      </c>
+      <c r="Q81" s="1" t="n">
+        <f aca="false">ROUND(P81,0)</f>
+        <v>2</v>
+      </c>
+      <c r="R81" s="1" t="s">
+        <v>300</v>
       </c>
     </row>
   </sheetData>
@@ -8051,7 +8119,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="B1" s="9"/>
       <c r="C1" s="9"/>
@@ -8067,10 +8135,10 @@
         <v>25</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8098,11 +8166,11 @@
       </c>
       <c r="C5" s="1" t="n">
         <f aca="false">COUNTIF(Evaluations!$A$2:$A$200,A5)</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D5" s="11" t="n">
         <f aca="false">AVERAGEIF(Evaluations!$A$2:$A$200,A5,Evaluations!$P$2:$P$200)</f>
-        <v>1.85339285714286</v>
+        <v>1.85725</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">

--- a/Fantasy_Grimdark_Scale_Fully_Scored.xlsx
+++ b/Fantasy_Grimdark_Scale_Fully_Scored.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="649" uniqueCount="304">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="656" uniqueCount="307">
   <si>
     <t xml:space="preserve">Fantasy Darkness Scale: Methodology</t>
   </si>
@@ -925,6 +925,15 @@
   </si>
   <si>
     <t xml:space="preserve">A mythic, single-villain fairy tale rather than anything institutional: Darkness's gothic menace and the stallion unicorn's death carry real atmospheric horror, but heroism is straightforward and decisive, and Lili's temptation is treated as innocence exploited rather than culpability.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The NeverEnding Story</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Michael Ende</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scored against the full novel, not just the 1984 film (which only adapts the first half): Artax's death and the Nothing's nihilism are real, but the book's second half — Bastian's own descent into cruelty once granted unlimited wish-power, and the hard-won cost of finding his way back to himself — adds real moral cynicism and redemption difficulty the film omits entirely.</t>
   </si>
   <si>
     <t xml:space="preserve">Fantasy Darkness Scale Summary</t>
@@ -2251,7 +2260,7 @@
                   <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>15</c:v>
+                  <c:v>16</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>16</c:v>
@@ -2283,11 +2292,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="17943322"/>
-        <c:axId val="22242778"/>
+        <c:axId val="25202197"/>
+        <c:axId val="61689998"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="17943322"/>
+        <c:axId val="25202197"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2332,7 +2341,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="22242778"/>
+        <c:crossAx val="61689998"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2340,7 +2349,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="22242778"/>
+        <c:axId val="61689998"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2385,7 +2394,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="17943322"/>
+        <c:crossAx val="25202197"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2642,9 +2651,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>605160</xdr:colOff>
+      <xdr:colOff>604800</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>184320</xdr:rowOff>
+      <xdr:rowOff>183960</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -2653,7 +2662,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="7518960" y="438120"/>
-        <a:ext cx="4885920" cy="3422880"/>
+        <a:ext cx="4885560" cy="3422520"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -3266,7 +3275,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:R81"/>
+  <dimension ref="A1:R82"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8"/>
@@ -7997,7 +8006,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="1" t="n">
         <v>2</v>
       </c>
@@ -8054,6 +8063,65 @@
       </c>
       <c r="R81" s="1" t="s">
         <v>300</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="E82" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="F82" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="G82" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="H82" s="1" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I82" s="1" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="J82" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K82" s="1" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="L82" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M82" s="1" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="N82" s="1" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="O82" s="1" t="n">
+        <f aca="false">H82*Methodology!$E$4+I82*Methodology!$E$5+J82*Methodology!$E$6+K82*Methodology!$E$7+L82*Methodology!$E$8+M82*Methodology!$E$9+N82*Methodology!$E$10</f>
+        <v>0.4925</v>
+      </c>
+      <c r="P82" s="1" t="n">
+        <f aca="false">1+(O82*2.25)</f>
+        <v>2.108125</v>
+      </c>
+      <c r="Q82" s="1" t="n">
+        <f aca="false">ROUND(P82,0)</f>
+        <v>2</v>
+      </c>
+      <c r="R82" s="1" t="s">
+        <v>303</v>
       </c>
     </row>
   </sheetData>
@@ -8119,7 +8187,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="B1" s="9"/>
       <c r="C1" s="9"/>
@@ -8135,10 +8203,10 @@
         <v>25</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8166,11 +8234,11 @@
       </c>
       <c r="C5" s="1" t="n">
         <f aca="false">COUNTIF(Evaluations!$A$2:$A$200,A5)</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D5" s="11" t="n">
         <f aca="false">AVERAGEIF(Evaluations!$A$2:$A$200,A5,Evaluations!$P$2:$P$200)</f>
-        <v>1.85725</v>
+        <v>1.8729296875</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">

--- a/Fantasy_Grimdark_Scale_Fully_Scored.xlsx
+++ b/Fantasy_Grimdark_Scale_Fully_Scored.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="656" uniqueCount="307">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="663" uniqueCount="311">
   <si>
     <t xml:space="preserve">Fantasy Darkness Scale: Methodology</t>
   </si>
@@ -934,6 +934,18 @@
   </si>
   <si>
     <t xml:space="preserve">Scored against the full novel, not just the 1984 film (which only adapts the first half): Artax's death and the Nothing's nihilism are real, but the book's second half — Bastian's own descent into cruelty once granted unlimited wish-power, and the hard-won cost of finding his way back to himself — adds real moral cynicism and redemption difficulty the film omits entirely.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shin Sekai Yori (From the New World)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Novel / Anime</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yusuke Kishi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A seemingly idyllic future society is built on secret child eugenics (killing children flagged as psychologically “unstable”) and the enslavement/extermination of the Queerats, who turn out to be humanity's own left-behind kin; the protagonists win a tactical victory but explicitly fail to dismantle the totalitarian system, which persists unchanged at the end.</t>
   </si>
   <si>
     <t xml:space="preserve">Fantasy Darkness Scale Summary</t>
@@ -2278,7 +2290,7 @@
                   <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>4</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>1</c:v>
@@ -2292,11 +2304,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="25202197"/>
-        <c:axId val="61689998"/>
+        <c:axId val="83786658"/>
+        <c:axId val="11467498"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="25202197"/>
+        <c:axId val="83786658"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2341,7 +2353,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="61689998"/>
+        <c:crossAx val="11467498"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2349,7 +2361,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="61689998"/>
+        <c:axId val="11467498"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2394,7 +2406,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="25202197"/>
+        <c:crossAx val="83786658"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2651,9 +2663,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>604800</xdr:colOff>
+      <xdr:colOff>604440</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>183960</xdr:rowOff>
+      <xdr:rowOff>183600</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -2662,7 +2674,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="7518960" y="438120"/>
-        <a:ext cx="4885560" cy="3422520"/>
+        <a:ext cx="4885200" cy="3422160"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -3275,7 +3287,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:R82"/>
+  <dimension ref="A1:R83"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8"/>
@@ -8065,7 +8077,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="1" t="n">
         <v>2</v>
       </c>
@@ -8122,6 +8134,65 @@
       </c>
       <c r="R82" s="1" t="s">
         <v>303</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="D83" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="E83" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="F83" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="G83" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="H83" s="1" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="I83" s="1" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J83" s="1" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K83" s="1" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L83" s="1" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="M83" s="1" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N83" s="1" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O83" s="1" t="n">
+        <f aca="false">H83*Methodology!$E$4+I83*Methodology!$E$5+J83*Methodology!$E$6+K83*Methodology!$E$7+L83*Methodology!$E$8+M83*Methodology!$E$9+N83*Methodology!$E$10</f>
+        <v>3.295</v>
+      </c>
+      <c r="P83" s="1" t="n">
+        <f aca="false">1+(O83*2.25)</f>
+        <v>8.41375</v>
+      </c>
+      <c r="Q83" s="1" t="n">
+        <f aca="false">ROUND(P83,0)</f>
+        <v>8</v>
+      </c>
+      <c r="R83" s="1" t="s">
+        <v>307</v>
       </c>
     </row>
   </sheetData>
@@ -8187,7 +8258,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="B1" s="9"/>
       <c r="C1" s="9"/>
@@ -8203,10 +8274,10 @@
         <v>25</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8330,11 +8401,11 @@
       </c>
       <c r="C11" s="1" t="n">
         <f aca="false">COUNTIF(Evaluations!$A$2:$A$200,A11)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D11" s="11" t="n">
         <f aca="false">AVERAGEIF(Evaluations!$A$2:$A$200,A11,Evaluations!$P$2:$P$200)</f>
-        <v>8.37859375</v>
+        <v>8.385625</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">

--- a/Fantasy_Grimdark_Scale_Fully_Scored.xlsx
+++ b/Fantasy_Grimdark_Scale_Fully_Scored.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="663" uniqueCount="311">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="670" uniqueCount="314">
   <si>
     <t xml:space="preserve">Fantasy Darkness Scale: Methodology</t>
   </si>
@@ -946,6 +946,15 @@
   </si>
   <si>
     <t xml:space="preserve">A seemingly idyllic future society is built on secret child eugenics (killing children flagged as psychologically “unstable”) and the enslavement/extermination of the Queerats, who turn out to be humanity's own left-behind kin; the protagonists win a tactical victory but explicitly fail to dismantle the totalitarian system, which persists unchanged at the end.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mushishi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yuki Urushibara</t>
+  </si>
+  <si>
+    <t xml:space="preserve">An anthology of quiet, often irreversible personal tragedy (permanent loss of a limb, a mother's death, lasting grief) rather than institutional darkness — there's no villain, no war, no system to critique, just impermanence met with care. Bittersweet Hopepunk: arguably the purest fit on this scale, since mortality-and-connection-anyway is the show's entire structure, not a framing device.</t>
   </si>
   <si>
     <t xml:space="preserve">Fantasy Darkness Scale Summary</t>
@@ -2272,7 +2281,7 @@
                   <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>16</c:v>
+                  <c:v>17</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>16</c:v>
@@ -2304,11 +2313,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="83786658"/>
-        <c:axId val="11467498"/>
+        <c:axId val="74498014"/>
+        <c:axId val="21620591"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="83786658"/>
+        <c:axId val="74498014"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2353,7 +2362,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="11467498"/>
+        <c:crossAx val="21620591"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2361,7 +2370,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="11467498"/>
+        <c:axId val="21620591"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2406,7 +2415,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="83786658"/>
+        <c:crossAx val="74498014"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2663,9 +2672,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>604440</xdr:colOff>
+      <xdr:colOff>604080</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>183600</xdr:rowOff>
+      <xdr:rowOff>183240</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -2674,7 +2683,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="7518960" y="438120"/>
-        <a:ext cx="4885200" cy="3422160"/>
+        <a:ext cx="4884840" cy="3421800"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -3287,7 +3296,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:R83"/>
+  <dimension ref="A1:R84"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8"/>
@@ -8136,7 +8145,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="1" t="n">
         <v>8</v>
       </c>
@@ -8193,6 +8202,65 @@
       </c>
       <c r="R83" s="1" t="s">
         <v>307</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E84" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="F84" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="G84" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="H84" s="1" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I84" s="1" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J84" s="1" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="K84" s="1" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L84" s="1" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M84" s="1" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N84" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="O84" s="1" t="n">
+        <f aca="false">H84*Methodology!$E$4+I84*Methodology!$E$5+J84*Methodology!$E$6+K84*Methodology!$E$7+L84*Methodology!$E$8+M84*Methodology!$E$9+N84*Methodology!$E$10</f>
+        <v>0.4675</v>
+      </c>
+      <c r="P84" s="1" t="n">
+        <f aca="false">1+(O84*2.25)</f>
+        <v>2.051875</v>
+      </c>
+      <c r="Q84" s="1" t="n">
+        <f aca="false">ROUND(P84,0)</f>
+        <v>2</v>
+      </c>
+      <c r="R84" s="1" t="s">
+        <v>310</v>
       </c>
     </row>
   </sheetData>
@@ -8258,7 +8326,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="B1" s="9"/>
       <c r="C1" s="9"/>
@@ -8274,10 +8342,10 @@
         <v>25</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8305,11 +8373,11 @@
       </c>
       <c r="C5" s="1" t="n">
         <f aca="false">COUNTIF(Evaluations!$A$2:$A$200,A5)</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D5" s="11" t="n">
         <f aca="false">AVERAGEIF(Evaluations!$A$2:$A$200,A5,Evaluations!$P$2:$P$200)</f>
-        <v>1.8729296875</v>
+        <v>1.88345588235294</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">

--- a/Fantasy_Grimdark_Scale_Fully_Scored.xlsx
+++ b/Fantasy_Grimdark_Scale_Fully_Scored.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="670" uniqueCount="314">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="677" uniqueCount="318">
   <si>
     <t xml:space="preserve">Fantasy Darkness Scale: Methodology</t>
   </si>
@@ -955,6 +955,18 @@
   </si>
   <si>
     <t xml:space="preserve">An anthology of quiet, often irreversible personal tragedy (permanent loss of a limb, a mother's death, lasting grief) rather than institutional darkness — there's no villain, no war, no system to critique, just impermanence met with care. Bittersweet Hopepunk: arguably the purest fit on this scale, since mortality-and-connection-anyway is the show's entire structure, not a framing device.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Record of Lodoss War</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Novels / Anime</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ryo Mizuno</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Classic D&amp;D-inspired epic fantasy: the Marmo invasion costs both warring kings their lives and the party its dwarf, Ghim, in the finale, and the Grey Witch Karla's whole modus operandi is centuries of orchestrating wars to keep any nation from growing too powerful — but the heroes still win a decisive, restorative victory, keeping it in Dragonlance's company rather than heavier territory.</t>
   </si>
   <si>
     <t xml:space="preserve">Fantasy Darkness Scale Summary</t>
@@ -2284,7 +2296,7 @@
                   <c:v>17</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>16</c:v>
+                  <c:v>17</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>21</c:v>
@@ -2313,11 +2325,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="74498014"/>
-        <c:axId val="21620591"/>
+        <c:axId val="54109588"/>
+        <c:axId val="55952649"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="74498014"/>
+        <c:axId val="54109588"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2362,7 +2374,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="21620591"/>
+        <c:crossAx val="55952649"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2370,7 +2382,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="21620591"/>
+        <c:axId val="55952649"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2415,7 +2427,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="74498014"/>
+        <c:crossAx val="54109588"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2672,9 +2684,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>604080</xdr:colOff>
+      <xdr:colOff>603720</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>183240</xdr:rowOff>
+      <xdr:rowOff>182880</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -2683,7 +2695,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="7518960" y="438120"/>
-        <a:ext cx="4884840" cy="3421800"/>
+        <a:ext cx="4884480" cy="3421440"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -3296,7 +3308,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:R84"/>
+  <dimension ref="A1:R85"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8"/>
@@ -8204,7 +8216,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="1" t="n">
         <v>2</v>
       </c>
@@ -8261,6 +8273,65 @@
       </c>
       <c r="R84" s="1" t="s">
         <v>310</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="E85" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="F85" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="G85" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="H85" s="1" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I85" s="1" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J85" s="1" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="K85" s="1" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="L85" s="1" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M85" s="1" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N85" s="1" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="O85" s="1" t="n">
+        <f aca="false">H85*Methodology!$E$4+I85*Methodology!$E$5+J85*Methodology!$E$6+K85*Methodology!$E$7+L85*Methodology!$E$8+M85*Methodology!$E$9+N85*Methodology!$E$10</f>
+        <v>0.775</v>
+      </c>
+      <c r="P85" s="1" t="n">
+        <f aca="false">1+(O85*2.25)</f>
+        <v>2.74375</v>
+      </c>
+      <c r="Q85" s="1" t="n">
+        <f aca="false">ROUND(P85,0)</f>
+        <v>3</v>
+      </c>
+      <c r="R85" s="1" t="s">
+        <v>314</v>
       </c>
     </row>
   </sheetData>
@@ -8326,7 +8397,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="B1" s="9"/>
       <c r="C1" s="9"/>
@@ -8342,10 +8413,10 @@
         <v>25</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8389,11 +8460,11 @@
       </c>
       <c r="C6" s="1" t="n">
         <f aca="false">COUNTIF(Evaluations!$A$2:$A$200,A6)</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D6" s="11" t="n">
         <f aca="false">AVERAGEIF(Evaluations!$A$2:$A$200,A6,Evaluations!$P$2:$P$200)</f>
-        <v>2.7342578125</v>
+        <v>2.73481617647059</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">

--- a/Fantasy_Grimdark_Scale_Fully_Scored.xlsx
+++ b/Fantasy_Grimdark_Scale_Fully_Scored.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="677" uniqueCount="318">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="684" uniqueCount="322">
   <si>
     <t xml:space="preserve">Fantasy Darkness Scale: Methodology</t>
   </si>
@@ -967,6 +967,18 @@
   </si>
   <si>
     <t xml:space="preserve">Classic D&amp;D-inspired epic fantasy: the Marmo invasion costs both warring kings their lives and the party its dwarf, Ghim, in the finale, and the Grey Witch Karla's whole modus operandi is centuries of orchestrating wars to keep any nation from growing too powerful — but the heroes still win a decisive, restorative victory, keeping it in Dragonlance's company rather than heavier territory.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Legend of Vox Machina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Critical Role</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TV-MA adult animation with real gore, a torture scene and on-screen child deaths, plus Percy's demon-fueled revenge arc and Vax'ildan's permanent death paying his soul to the Raven Queen — but the found-family heart, crude comedy, and consistently successful heroism (Whitestone liberated, Percy's darkness overcome) keep hope structurally dominant.</t>
   </si>
   <si>
     <t xml:space="preserve">Fantasy Darkness Scale Summary</t>
@@ -2299,7 +2311,7 @@
                   <c:v>17</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>21</c:v>
+                  <c:v>22</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>9</c:v>
@@ -2325,11 +2337,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="54109588"/>
-        <c:axId val="55952649"/>
+        <c:axId val="72794581"/>
+        <c:axId val="93301847"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="54109588"/>
+        <c:axId val="72794581"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2374,7 +2386,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="55952649"/>
+        <c:crossAx val="93301847"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2382,7 +2394,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="55952649"/>
+        <c:axId val="93301847"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2427,7 +2439,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="54109588"/>
+        <c:crossAx val="72794581"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2684,9 +2696,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>603720</xdr:colOff>
+      <xdr:colOff>603360</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>182880</xdr:rowOff>
+      <xdr:rowOff>182520</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -2695,7 +2707,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="7518960" y="438120"/>
-        <a:ext cx="4884480" cy="3421440"/>
+        <a:ext cx="4884120" cy="3421080"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -3308,7 +3320,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:R85"/>
+  <dimension ref="A1:R86"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8"/>
@@ -8275,7 +8287,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="1" t="n">
         <v>3</v>
       </c>
@@ -8332,6 +8344,65 @@
       </c>
       <c r="R85" s="1" t="s">
         <v>314</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="D86" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="E86" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="F86" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="G86" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="H86" s="1" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I86" s="1" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J86" s="1" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="K86" s="1" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="L86" s="1" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="M86" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N86" s="1" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="O86" s="1" t="n">
+        <f aca="false">H86*Methodology!$E$4+I86*Methodology!$E$5+J86*Methodology!$E$6+K86*Methodology!$E$7+L86*Methodology!$E$8+M86*Methodology!$E$9+N86*Methodology!$E$10</f>
+        <v>1.22</v>
+      </c>
+      <c r="P86" s="1" t="n">
+        <f aca="false">1+(O86*2.25)</f>
+        <v>3.745</v>
+      </c>
+      <c r="Q86" s="1" t="n">
+        <f aca="false">ROUND(P86,0)</f>
+        <v>4</v>
+      </c>
+      <c r="R86" s="1" t="s">
+        <v>318</v>
       </c>
     </row>
   </sheetData>
@@ -8397,7 +8468,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="B1" s="9"/>
       <c r="C1" s="9"/>
@@ -8413,10 +8484,10 @@
         <v>25</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8476,11 +8547,11 @@
       </c>
       <c r="C7" s="1" t="n">
         <f aca="false">COUNTIF(Evaluations!$A$2:$A$200,A7)</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D7" s="11" t="n">
         <f aca="false">AVERAGEIF(Evaluations!$A$2:$A$200,A7,Evaluations!$P$2:$P$200)</f>
-        <v>3.77232142857143</v>
+        <v>3.77107954545455</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">

--- a/Fantasy_Grimdark_Scale_Fully_Scored.xlsx
+++ b/Fantasy_Grimdark_Scale_Fully_Scored.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="684" uniqueCount="322">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="691" uniqueCount="325">
   <si>
     <t xml:space="preserve">Fantasy Darkness Scale: Methodology</t>
   </si>
@@ -979,6 +979,15 @@
   </si>
   <si>
     <t xml:space="preserve">TV-MA adult animation with real gore, a torture scene and on-screen child deaths, plus Percy's demon-fueled revenge arc and Vax'ildan's permanent death paying his soul to the Raven Queen — but the found-family heart, crude comedy, and consistently successful heroism (Whitestone liberated, Percy's darkness overcome) keep hope structurally dominant.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Nightmare Before Christmas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tim Burton / Henry Selick</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gothic cotton candy: Oogie Boogie's sadistic gambling with Santa's life gives it real (if comedic) villain menace the gentlest Ghibli films don't have, but the whimsical Halloween Town community is fundamentally kind, Jack's mistake is quickly and fully undone, and the ending restores everything with romance blooming.</t>
   </si>
   <si>
     <t xml:space="preserve">Fantasy Darkness Scale Summary</t>
@@ -2302,7 +2311,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>4</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>17</c:v>
@@ -2337,11 +2346,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="72794581"/>
-        <c:axId val="93301847"/>
+        <c:axId val="27111044"/>
+        <c:axId val="81977665"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="72794581"/>
+        <c:axId val="27111044"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2386,7 +2395,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="93301847"/>
+        <c:crossAx val="81977665"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2394,7 +2403,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="93301847"/>
+        <c:axId val="81977665"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2439,7 +2448,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="72794581"/>
+        <c:crossAx val="27111044"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2696,9 +2705,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>603360</xdr:colOff>
+      <xdr:colOff>603000</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>182520</xdr:rowOff>
+      <xdr:rowOff>182160</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -2707,7 +2716,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="7518960" y="438120"/>
-        <a:ext cx="4884120" cy="3421080"/>
+        <a:ext cx="4883760" cy="3420720"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -3320,7 +3329,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:R86"/>
+  <dimension ref="A1:R87"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8"/>
@@ -8346,7 +8355,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="1" t="n">
         <v>4</v>
       </c>
@@ -8403,6 +8412,65 @@
       </c>
       <c r="R86" s="1" t="s">
         <v>318</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="D87" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E87" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="F87" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="G87" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="H87" s="1" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I87" s="1" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="J87" s="1" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="K87" s="1" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L87" s="1" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="M87" s="1" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="N87" s="1" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="O87" s="1" t="n">
+        <f aca="false">H87*Methodology!$E$4+I87*Methodology!$E$5+J87*Methodology!$E$6+K87*Methodology!$E$7+L87*Methodology!$E$8+M87*Methodology!$E$9+N87*Methodology!$E$10</f>
+        <v>0.205</v>
+      </c>
+      <c r="P87" s="1" t="n">
+        <f aca="false">1+(O87*2.25)</f>
+        <v>1.46125</v>
+      </c>
+      <c r="Q87" s="1" t="n">
+        <f aca="false">ROUND(P87,0)</f>
+        <v>1</v>
+      </c>
+      <c r="R87" s="1" t="s">
+        <v>321</v>
       </c>
     </row>
   </sheetData>
@@ -8468,7 +8536,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="B1" s="9"/>
       <c r="C1" s="9"/>
@@ -8484,10 +8552,10 @@
         <v>25</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8499,11 +8567,11 @@
       </c>
       <c r="C4" s="1" t="n">
         <f aca="false">COUNTIF(Evaluations!$A$2:$A$200,A4)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D4" s="11" t="n">
         <f aca="false">AVERAGEIF(Evaluations!$A$2:$A$200,A4,Evaluations!$P$2:$P$200)</f>
-        <v>1.15890625</v>
+        <v>1.219375</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">

--- a/Fantasy_Grimdark_Scale_Fully_Scored.xlsx
+++ b/Fantasy_Grimdark_Scale_Fully_Scored.xlsx
@@ -987,7 +987,7 @@
     <t xml:space="preserve">Tim Burton / Henry Selick</t>
   </si>
   <si>
-    <t xml:space="preserve">Gothic cotton candy: Oogie Boogie's sadistic gambling with Santa's life gives it real (if comedic) villain menace the gentlest Ghibli films don't have, but the whimsical Halloween Town community is fundamentally kind, Jack's mistake is quickly and fully undone, and the ending restores everything with romance blooming.</t>
+    <t xml:space="preserve">Corrected from an earlier tier-1 placement: the pervasive Halloween Town horror aesthetic (skeleton/monster designs throughout, Sally's repeated self-dismemberment, Oogie Boogie sadistically gambling with Santa's life, children traumatized by monstrous gifts) is a lot of visible, disturbing content for a film whose plot ultimately resolves safely — Explicit Darkness was underweighted the first time.</t>
   </si>
   <si>
     <t xml:space="preserve">Fantasy Darkness Scale Summary</t>
@@ -2311,10 +2311,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>5</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>17</c:v>
+                  <c:v>18</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>17</c:v>
@@ -2346,11 +2346,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="27111044"/>
-        <c:axId val="81977665"/>
+        <c:axId val="39755150"/>
+        <c:axId val="83895924"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="27111044"/>
+        <c:axId val="39755150"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2395,7 +2395,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="81977665"/>
+        <c:crossAx val="83895924"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2403,7 +2403,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="81977665"/>
+        <c:axId val="83895924"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2448,7 +2448,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="27111044"/>
+        <c:crossAx val="39755150"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2705,9 +2705,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>603000</xdr:colOff>
+      <xdr:colOff>602640</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>182160</xdr:rowOff>
+      <xdr:rowOff>181800</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -2716,7 +2716,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="7518960" y="438120"/>
-        <a:ext cx="4883760" cy="3420720"/>
+        <a:ext cx="4883400" cy="3420360"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -8414,12 +8414,12 @@
         <v>318</v>
       </c>
     </row>
-    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>319</v>
@@ -8434,40 +8434,40 @@
         <v>61</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H87" s="1" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I87" s="1" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J87" s="1" t="n">
         <v>0.2</v>
       </c>
-      <c r="I87" s="1" t="n">
+      <c r="K87" s="1" t="n">
         <v>0.15</v>
       </c>
-      <c r="J87" s="1" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="K87" s="1" t="n">
-        <v>0.1</v>
-      </c>
       <c r="L87" s="1" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="M87" s="1" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="N87" s="1" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="O87" s="1" t="n">
         <f aca="false">H87*Methodology!$E$4+I87*Methodology!$E$5+J87*Methodology!$E$6+K87*Methodology!$E$7+L87*Methodology!$E$8+M87*Methodology!$E$9+N87*Methodology!$E$10</f>
-        <v>0.205</v>
+        <v>0.3175</v>
       </c>
       <c r="P87" s="1" t="n">
         <f aca="false">1+(O87*2.25)</f>
-        <v>1.46125</v>
+        <v>1.714375</v>
       </c>
       <c r="Q87" s="1" t="n">
         <f aca="false">ROUND(P87,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R87" s="1" t="s">
         <v>321</v>
@@ -8567,11 +8567,11 @@
       </c>
       <c r="C4" s="1" t="n">
         <f aca="false">COUNTIF(Evaluations!$A$2:$A$200,A4)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D4" s="11" t="n">
         <f aca="false">AVERAGEIF(Evaluations!$A$2:$A$200,A4,Evaluations!$P$2:$P$200)</f>
-        <v>1.219375</v>
+        <v>1.15890625</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8583,11 +8583,11 @@
       </c>
       <c r="C5" s="1" t="n">
         <f aca="false">COUNTIF(Evaluations!$A$2:$A$200,A5)</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D5" s="11" t="n">
         <f aca="false">AVERAGEIF(Evaluations!$A$2:$A$200,A5,Evaluations!$P$2:$P$200)</f>
-        <v>1.88345588235294</v>
+        <v>1.8740625</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">

--- a/Fantasy_Grimdark_Scale_Fully_Scored.xlsx
+++ b/Fantasy_Grimdark_Scale_Fully_Scored.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="691" uniqueCount="325">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="698" uniqueCount="328">
   <si>
     <t xml:space="preserve">Fantasy Darkness Scale: Methodology</t>
   </si>
@@ -988,6 +988,15 @@
   </si>
   <si>
     <t xml:space="preserve">Corrected from an earlier tier-1 placement: the pervasive Halloween Town horror aesthetic (skeleton/monster designs throughout, Sally's repeated self-dismemberment, Oogie Boogie sadistically gambling with Santa's life, children traumatized by monstrous gifts) is a lot of visible, disturbing content for a film whose plot ultimately resolves safely — Explicit Darkness was underweighted the first time.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Willow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ron Howard / George Lucas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Queen Bavmorda's decree to imprison every pregnant woman in her kingdom to prevent a prophesied downfall is genuinely severe institutional cruelty, and Airk dies in battle — but the comic-tinged transformation magic, Sorsha's clean redemption arc, and Bavmorda's almost ironic self-inflicted defeat keep the register close to Narnia and Castle in the Sky.</t>
   </si>
   <si>
     <t xml:space="preserve">Fantasy Darkness Scale Summary</t>
@@ -2314,7 +2323,7 @@
                   <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>18</c:v>
+                  <c:v>19</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>17</c:v>
@@ -2346,11 +2355,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="39755150"/>
-        <c:axId val="83895924"/>
+        <c:axId val="51503892"/>
+        <c:axId val="91564592"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="39755150"/>
+        <c:axId val="51503892"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2395,7 +2404,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="83895924"/>
+        <c:crossAx val="91564592"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2403,7 +2412,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="83895924"/>
+        <c:axId val="91564592"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2448,7 +2457,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="39755150"/>
+        <c:crossAx val="51503892"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2705,9 +2714,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>602640</xdr:colOff>
+      <xdr:colOff>602280</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>181800</xdr:rowOff>
+      <xdr:rowOff>181440</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -2716,7 +2725,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="7518960" y="438120"/>
-        <a:ext cx="4883400" cy="3420360"/>
+        <a:ext cx="4883040" cy="3420000"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -3329,7 +3338,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:R87"/>
+  <dimension ref="A1:R88"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8"/>
@@ -8471,6 +8480,65 @@
       </c>
       <c r="R87" s="1" t="s">
         <v>321</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E88" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="F88" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="G88" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="H88" s="1" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="I88" s="1" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="J88" s="1" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="K88" s="1" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="L88" s="1" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M88" s="1" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="N88" s="1" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="O88" s="1" t="n">
+        <f aca="false">H88*Methodology!$E$4+I88*Methodology!$E$5+J88*Methodology!$E$6+K88*Methodology!$E$7+L88*Methodology!$E$8+M88*Methodology!$E$9+N88*Methodology!$E$10</f>
+        <v>0.3775</v>
+      </c>
+      <c r="P88" s="1" t="n">
+        <f aca="false">1+(O88*2.25)</f>
+        <v>1.849375</v>
+      </c>
+      <c r="Q88" s="1" t="n">
+        <f aca="false">ROUND(P88,0)</f>
+        <v>2</v>
+      </c>
+      <c r="R88" s="1" t="s">
+        <v>324</v>
       </c>
     </row>
   </sheetData>
@@ -8536,7 +8604,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="B1" s="9"/>
       <c r="C1" s="9"/>
@@ -8552,10 +8620,10 @@
         <v>25</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8583,11 +8651,11 @@
       </c>
       <c r="C5" s="1" t="n">
         <f aca="false">COUNTIF(Evaluations!$A$2:$A$200,A5)</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D5" s="11" t="n">
         <f aca="false">AVERAGEIF(Evaluations!$A$2:$A$200,A5,Evaluations!$P$2:$P$200)</f>
-        <v>1.8740625</v>
+        <v>1.87276315789474</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
